--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C93AD65-CCA7-4E07-9D7A-EC11A5491106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DC494-BA15-44CA-8615-17E2C834DEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="255">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -846,6 +846,38 @@
   </si>
   <si>
     <t>[{class:"TroopSkillCalculateAttackBack", value:200, isDefender:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1},{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[1,2,3,4,5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:0}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[6]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[7]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6},{class:"SkillIsNormalSkill", result:1} ] }}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1002,7 +1034,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1046,9 +1078,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1057,6 +1086,21 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1369,21 +1413,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:I104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="254.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="254.6328125" style="19" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1395,9 +1439,9 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1407,9 +1451,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1429,11 +1473,11 @@
         <v>12</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1455,11 +1499,11 @@
       <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="20" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>1</v>
       </c>
@@ -1478,8 +1522,11 @@
       <c r="G5" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H5" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="11">
         <v>2</v>
@@ -1499,8 +1546,11 @@
       <c r="G6" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H6" s="21" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -1519,8 +1569,11 @@
       <c r="G7" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H7" s="21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -1539,8 +1592,11 @@
       <c r="G8" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H8" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -1559,8 +1615,11 @@
       <c r="G9" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H9" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -1579,8 +1638,11 @@
       <c r="G10" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H10" s="21" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
@@ -1600,7 +1662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -1619,8 +1681,11 @@
       <c r="G12" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H12" s="21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -1640,7 +1705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -1660,7 +1725,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="11">
         <v>11</v>
       </c>
@@ -1680,7 +1745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -1700,7 +1765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="11">
         <v>13</v>
       </c>
@@ -1720,7 +1785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -1740,7 +1805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -1760,7 +1825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="11">
         <v>16</v>
       </c>
@@ -1779,8 +1844,11 @@
       <c r="G20" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="H20" s="21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="11">
         <v>17</v>
       </c>
@@ -1800,7 +1868,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="11">
         <v>18</v>
       </c>
@@ -1820,7 +1888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -1840,7 +1908,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -1860,7 +1928,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -1880,7 +1948,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -1900,7 +1968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="11">
         <v>23</v>
       </c>
@@ -1920,7 +1988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="11">
         <v>24</v>
       </c>
@@ -1940,7 +2008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="11">
         <v>25</v>
       </c>
@@ -1960,7 +2028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="11">
         <v>26</v>
       </c>
@@ -1980,7 +2048,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2000,7 +2068,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2020,7 +2088,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2040,7 +2108,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2060,7 +2128,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2080,7 +2148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2100,7 +2168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2120,7 +2188,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2140,352 +2208,352 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="2:8" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="17">
+    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="16">
         <v>35</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E39" s="17">
-        <v>2</v>
-      </c>
-      <c r="F39" s="17">
-        <v>2</v>
-      </c>
-      <c r="G39" s="17" t="s">
+      <c r="E39" s="16">
+        <v>2</v>
+      </c>
+      <c r="F39" s="16">
+        <v>2</v>
+      </c>
+      <c r="G39" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="21" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="17">
+    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="16">
         <v>36</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="17">
-        <v>2</v>
-      </c>
-      <c r="F40" s="17">
-        <v>2</v>
-      </c>
-      <c r="G40" s="17" t="s">
+      <c r="E40" s="16">
+        <v>2</v>
+      </c>
+      <c r="F40" s="16">
+        <v>2</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="H40" s="21" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="17">
+    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="16">
         <v>37</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E41" s="17">
-        <v>2</v>
-      </c>
-      <c r="F41" s="17">
-        <v>2</v>
-      </c>
-      <c r="G41" s="17" t="s">
+      <c r="E41" s="16">
+        <v>2</v>
+      </c>
+      <c r="F41" s="16">
+        <v>2</v>
+      </c>
+      <c r="G41" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="21" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="42" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="17">
+    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="16">
         <v>38</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="17">
-        <v>2</v>
-      </c>
-      <c r="F42" s="17">
-        <v>2</v>
-      </c>
-      <c r="G42" s="17" t="s">
+      <c r="E42" s="16">
+        <v>2</v>
+      </c>
+      <c r="F42" s="16">
+        <v>2</v>
+      </c>
+      <c r="G42" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="18" t="s">
+      <c r="H42" s="21" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="17">
+    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="16">
         <v>39</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E43" s="17">
-        <v>2</v>
-      </c>
-      <c r="F43" s="17">
-        <v>2</v>
-      </c>
-      <c r="G43" s="17" t="s">
+      <c r="E43" s="16">
+        <v>2</v>
+      </c>
+      <c r="F43" s="16">
+        <v>2</v>
+      </c>
+      <c r="G43" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="18" t="s">
+      <c r="H43" s="21" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="17">
+    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="16">
         <v>40</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="17">
-        <v>3</v>
-      </c>
-      <c r="F44" s="17">
-        <v>2</v>
-      </c>
-      <c r="G44" s="17" t="s">
+      <c r="E44" s="16">
+        <v>3</v>
+      </c>
+      <c r="F44" s="16">
+        <v>2</v>
+      </c>
+      <c r="G44" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="18" t="s">
+      <c r="H44" s="21" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="17">
+    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="16">
         <v>41</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="16">
         <v>4</v>
       </c>
-      <c r="F45" s="17">
-        <v>2</v>
-      </c>
-      <c r="G45" s="17" t="s">
+      <c r="F45" s="16">
+        <v>2</v>
+      </c>
+      <c r="G45" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H45" s="18" t="s">
+      <c r="H45" s="21" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="17">
+    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="16">
         <v>42</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="17">
-        <v>3</v>
-      </c>
-      <c r="F46" s="17">
-        <v>2</v>
-      </c>
-      <c r="G46" s="17" t="s">
+      <c r="E46" s="16">
+        <v>3</v>
+      </c>
+      <c r="F46" s="16">
+        <v>2</v>
+      </c>
+      <c r="G46" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H46" s="18" t="s">
+      <c r="H46" s="21" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="17">
+    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="16">
         <v>43</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="17">
-        <v>3</v>
-      </c>
-      <c r="F47" s="17">
-        <v>2</v>
-      </c>
-      <c r="G47" s="17" t="s">
+      <c r="E47" s="16">
+        <v>3</v>
+      </c>
+      <c r="F47" s="16">
+        <v>2</v>
+      </c>
+      <c r="G47" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="18" t="s">
+      <c r="H47" s="21" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="48" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="17">
+    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="16">
         <v>44</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="17">
-        <v>3</v>
-      </c>
-      <c r="F48" s="17">
-        <v>2</v>
-      </c>
-      <c r="G48" s="17" t="s">
+      <c r="E48" s="16">
+        <v>3</v>
+      </c>
+      <c r="F48" s="16">
+        <v>2</v>
+      </c>
+      <c r="G48" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="18" t="s">
+      <c r="H48" s="21" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="17">
+    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="16">
         <v>45</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E49" s="17">
-        <v>3</v>
-      </c>
-      <c r="F49" s="17">
-        <v>2</v>
-      </c>
-      <c r="G49" s="17" t="s">
+      <c r="E49" s="16">
+        <v>3</v>
+      </c>
+      <c r="F49" s="16">
+        <v>2</v>
+      </c>
+      <c r="G49" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H49" s="18" t="s">
+      <c r="H49" s="21" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="17">
+    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="16">
         <v>46</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E50" s="17">
-        <v>3</v>
-      </c>
-      <c r="F50" s="17">
-        <v>2</v>
-      </c>
-      <c r="G50" s="17" t="s">
+      <c r="E50" s="16">
+        <v>3</v>
+      </c>
+      <c r="F50" s="16">
+        <v>2</v>
+      </c>
+      <c r="G50" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="18" t="s">
+      <c r="H50" s="21" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="17">
+    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="16">
         <v>47</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E51" s="17">
-        <v>3</v>
-      </c>
-      <c r="F51" s="17">
-        <v>2</v>
-      </c>
-      <c r="G51" s="17" t="s">
+      <c r="E51" s="16">
+        <v>3</v>
+      </c>
+      <c r="F51" s="16">
+        <v>2</v>
+      </c>
+      <c r="G51" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H51" s="18" t="s">
+      <c r="H51" s="21" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="17">
+    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="16">
         <v>48</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E52" s="17">
-        <v>3</v>
-      </c>
-      <c r="F52" s="17">
-        <v>2</v>
-      </c>
-      <c r="G52" s="17" t="s">
+      <c r="E52" s="16">
+        <v>3</v>
+      </c>
+      <c r="F52" s="16">
+        <v>2</v>
+      </c>
+      <c r="G52" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H52" s="18" t="s">
+      <c r="H52" s="21" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="17">
+    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="16">
         <v>49</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="16">
         <v>4</v>
       </c>
-      <c r="F53" s="17">
-        <v>2</v>
-      </c>
-      <c r="G53" s="17" t="s">
+      <c r="F53" s="16">
+        <v>2</v>
+      </c>
+      <c r="G53" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H53" s="18" t="s">
+      <c r="H53" s="21" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="11">
         <v>50</v>
       </c>
@@ -2498,14 +2566,14 @@
       <c r="E54" s="11">
         <v>3</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="15">
         <v>2</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2518,15 +2586,15 @@
       <c r="E55" s="9">
         <v>2</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="15">
         <v>2</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H55" s="15"/>
-    </row>
-    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H55" s="22"/>
+    </row>
+    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2539,15 +2607,15 @@
       <c r="E56" s="9">
         <v>2</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="15">
         <v>2</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H56" s="15"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="H56" s="22"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -2567,7 +2635,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="11">
         <v>54</v>
       </c>
@@ -2587,7 +2655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="11">
         <v>55</v>
       </c>
@@ -2607,7 +2675,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="11">
         <v>56</v>
       </c>
@@ -2627,7 +2695,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="11">
         <v>57</v>
       </c>
@@ -2647,7 +2715,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="11">
         <v>58</v>
       </c>
@@ -2667,7 +2735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" s="11">
         <v>59</v>
       </c>
@@ -2687,7 +2755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="11">
         <v>60</v>
       </c>
@@ -2707,7 +2775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="11">
         <v>61</v>
       </c>
@@ -2727,33 +2795,33 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B66" s="17">
+    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="16">
         <v>62</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="16">
         <v>4</v>
       </c>
-      <c r="F66" s="17">
+      <c r="F66" s="16">
         <v>4</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G66" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="H66" s="18" t="s">
+      <c r="H66" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="I66" s="18" t="s">
+      <c r="I66" s="17" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="11">
         <v>63</v>
       </c>
@@ -2773,7 +2841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="11">
         <v>64</v>
       </c>
@@ -2793,7 +2861,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="11">
         <v>65</v>
       </c>
@@ -2813,7 +2881,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="11">
         <v>66</v>
       </c>
@@ -2833,7 +2901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="11">
         <v>67</v>
       </c>
@@ -2853,7 +2921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="11">
         <v>68</v>
       </c>
@@ -2873,7 +2941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -2893,7 +2961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -2913,7 +2981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -2933,7 +3001,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -2953,7 +3021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="11">
         <v>73</v>
       </c>
@@ -2973,7 +3041,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="11">
         <v>74</v>
       </c>
@@ -2993,7 +3061,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="11">
         <v>75</v>
       </c>
@@ -3013,7 +3081,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3032,9 +3100,9 @@
       <c r="G80" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H80" s="15"/>
-    </row>
-    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H80" s="22"/>
+    </row>
+    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3053,9 +3121,9 @@
       <c r="G81" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H81" s="15"/>
-    </row>
-    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H81" s="22"/>
+    </row>
+    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3074,9 +3142,9 @@
       <c r="G82" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H82" s="15"/>
-    </row>
-    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H82" s="22"/>
+    </row>
+    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3095,124 +3163,124 @@
       <c r="G83" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H83" s="15"/>
-    </row>
-    <row r="84" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="17">
+      <c r="H83" s="22"/>
+    </row>
+    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="16">
         <v>80</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="E84" s="17">
-        <v>2</v>
-      </c>
-      <c r="F84" s="18" t="s">
+      <c r="E84" s="16">
+        <v>2</v>
+      </c>
+      <c r="F84" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="G84" s="17" t="s">
+      <c r="G84" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H84" s="18" t="s">
+      <c r="H84" s="21" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B85" s="17">
+    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="16">
         <v>81</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E85" s="17">
-        <v>2</v>
-      </c>
-      <c r="F85" s="18" t="s">
+      <c r="E85" s="16">
+        <v>2</v>
+      </c>
+      <c r="F85" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="G85" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H85" s="18" t="s">
+      <c r="H85" s="21" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B86" s="17">
+    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="16">
         <v>82</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="17">
-        <v>2</v>
-      </c>
-      <c r="F86" s="18" t="s">
+      <c r="E86" s="16">
+        <v>2</v>
+      </c>
+      <c r="F86" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="G86" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H86" s="18" t="s">
+      <c r="H86" s="21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="87" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B87" s="17">
+    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="16">
         <v>83</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E87" s="17">
-        <v>2</v>
-      </c>
-      <c r="F87" s="18" t="s">
+      <c r="E87" s="16">
+        <v>2</v>
+      </c>
+      <c r="F87" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="G87" s="17" t="s">
+      <c r="G87" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H87" s="18" t="s">
+      <c r="H87" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B88" s="17">
+    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="16">
         <v>84</v>
       </c>
-      <c r="C88" s="17" t="s">
+      <c r="C88" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="E88" s="17">
-        <v>2</v>
-      </c>
-      <c r="F88" s="18" t="s">
+      <c r="E88" s="16">
+        <v>2</v>
+      </c>
+      <c r="F88" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="G88" s="17" t="s">
+      <c r="G88" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H88" s="18" t="s">
+      <c r="H88" s="21" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3231,9 +3299,9 @@
       <c r="G89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H89" s="15"/>
-    </row>
-    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H89" s="22"/>
+    </row>
+    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3252,9 +3320,9 @@
       <c r="G90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H90" s="15"/>
-    </row>
-    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H90" s="22"/>
+    </row>
+    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3273,9 +3341,9 @@
       <c r="G91" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H91" s="15"/>
-    </row>
-    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H91" s="22"/>
+    </row>
+    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3294,9 +3362,9 @@
       <c r="G92" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H92" s="2"/>
-    </row>
-    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H92" s="19"/>
+    </row>
+    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3315,9 +3383,9 @@
       <c r="G93" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H93" s="15"/>
-    </row>
-    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H93" s="22"/>
+    </row>
+    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3336,9 +3404,9 @@
       <c r="G94" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H94" s="15"/>
-    </row>
-    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H94" s="22"/>
+    </row>
+    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3357,9 +3425,9 @@
       <c r="G95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H95" s="15"/>
-    </row>
-    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H95" s="22"/>
+    </row>
+    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3378,9 +3446,9 @@
       <c r="G96" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H96" s="15"/>
-    </row>
-    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H96" s="22"/>
+    </row>
+    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3399,9 +3467,9 @@
       <c r="G97" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H97" s="15"/>
-    </row>
-    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H97" s="22"/>
+    </row>
+    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3420,9 +3488,9 @@
       <c r="G98" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H98" s="15"/>
-    </row>
-    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H98" s="22"/>
+    </row>
+    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -3441,9 +3509,9 @@
       <c r="G99" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H99" s="15"/>
-    </row>
-    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H99" s="22"/>
+    </row>
+    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -3462,9 +3530,9 @@
       <c r="G100" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H100" s="15"/>
-    </row>
-    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H100" s="22"/>
+    </row>
+    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -3483,9 +3551,9 @@
       <c r="G101" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H101" s="15"/>
-    </row>
-    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H101" s="22"/>
+    </row>
+    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -3504,9 +3572,9 @@
       <c r="G102" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H102" s="15"/>
-    </row>
-    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H102" s="22"/>
+    </row>
+    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -3525,9 +3593,9 @@
       <c r="G103" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H103" s="15"/>
-    </row>
-    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H103" s="22"/>
+    </row>
+    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>
@@ -3546,7 +3614,7 @@
       <c r="G104" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="H104" s="15"/>
+      <c r="H104" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DC494-BA15-44CA-8615-17E2C834DEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FB938A-5325-41D1-BC57-0EC6965EFB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="257">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -877,7 +877,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6},{class:"SkillIsNormalSkill", result:1} ] }}]</t>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[27], result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1034,7 +1042,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1100,6 +1108,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1413,21 +1430,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:I104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="254.6328125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="254.625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1441,7 +1458,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="18"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1453,7 +1470,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="19"/>
     </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1477,7 +1494,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1503,7 +1520,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B5" s="12">
         <v>1</v>
       </c>
@@ -1526,7 +1543,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="14"/>
       <c r="B6" s="11">
         <v>2</v>
@@ -1550,7 +1567,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -1573,7 +1590,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -1596,7 +1613,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -1619,7 +1636,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -1642,27 +1659,28 @@
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+    <row r="11" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="9">
         <v>7</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="11">
-        <v>2</v>
-      </c>
-      <c r="F11" s="12">
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+      <c r="F11" s="24">
         <v>1</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="25"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -1685,27 +1703,28 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="11">
+    <row r="13" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="9">
         <v>9</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="11">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="E13" s="9">
+        <v>2</v>
+      </c>
+      <c r="F13" s="24">
         <v>1</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -1725,7 +1744,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
         <v>11</v>
       </c>
@@ -1745,7 +1764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -1765,7 +1784,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
         <v>13</v>
       </c>
@@ -1785,7 +1804,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -1805,7 +1824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -1825,7 +1844,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="11">
         <v>16</v>
       </c>
@@ -1845,10 +1864,10 @@
         <v>35</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="11">
         <v>17</v>
       </c>
@@ -1867,8 +1886,11 @@
       <c r="G21" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="11">
         <v>18</v>
       </c>
@@ -1887,8 +1909,11 @@
       <c r="G22" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -1908,7 +1933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -1928,7 +1953,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -1948,7 +1973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -1968,7 +1993,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="11">
         <v>23</v>
       </c>
@@ -1988,7 +2013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="11">
         <v>24</v>
       </c>
@@ -2008,7 +2033,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="11">
         <v>25</v>
       </c>
@@ -2028,7 +2053,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="11">
         <v>26</v>
       </c>
@@ -2048,7 +2073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2068,7 +2093,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2088,7 +2113,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2108,7 +2133,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2128,7 +2153,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2148,7 +2173,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2168,7 +2193,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2188,7 +2213,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2208,7 +2233,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="16">
         <v>35</v>
       </c>
@@ -2231,7 +2256,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="16">
         <v>36</v>
       </c>
@@ -2254,7 +2279,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="16">
         <v>37</v>
       </c>
@@ -2277,7 +2302,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="16">
         <v>38</v>
       </c>
@@ -2300,7 +2325,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="16">
         <v>39</v>
       </c>
@@ -2323,7 +2348,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="16">
         <v>40</v>
       </c>
@@ -2346,7 +2371,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16">
         <v>41</v>
       </c>
@@ -2369,7 +2394,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="16">
         <v>42</v>
       </c>
@@ -2392,7 +2417,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="16">
         <v>43</v>
       </c>
@@ -2415,7 +2440,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="16">
         <v>44</v>
       </c>
@@ -2438,7 +2463,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="16">
         <v>45</v>
       </c>
@@ -2461,7 +2486,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="16">
         <v>46</v>
       </c>
@@ -2484,7 +2509,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="16">
         <v>47</v>
       </c>
@@ -2507,7 +2532,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="16">
         <v>48</v>
       </c>
@@ -2530,7 +2555,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="16">
         <v>49</v>
       </c>
@@ -2553,7 +2578,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="11">
         <v>50</v>
       </c>
@@ -2573,7 +2598,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2594,7 +2619,7 @@
       </c>
       <c r="H55" s="22"/>
     </row>
-    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2615,7 +2640,7 @@
       </c>
       <c r="H56" s="22"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -2635,7 +2660,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B58" s="11">
         <v>54</v>
       </c>
@@ -2655,7 +2680,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B59" s="11">
         <v>55</v>
       </c>
@@ -2675,7 +2700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B60" s="11">
         <v>56</v>
       </c>
@@ -2695,7 +2720,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B61" s="11">
         <v>57</v>
       </c>
@@ -2715,7 +2740,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B62" s="11">
         <v>58</v>
       </c>
@@ -2735,7 +2760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B63" s="11">
         <v>59</v>
       </c>
@@ -2755,7 +2780,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B64" s="11">
         <v>60</v>
       </c>
@@ -2775,7 +2800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B65" s="11">
         <v>61</v>
       </c>
@@ -2795,7 +2820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="16">
         <v>62</v>
       </c>
@@ -2821,7 +2846,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B67" s="11">
         <v>63</v>
       </c>
@@ -2841,7 +2866,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B68" s="11">
         <v>64</v>
       </c>
@@ -2861,7 +2886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B69" s="11">
         <v>65</v>
       </c>
@@ -2881,7 +2906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B70" s="11">
         <v>66</v>
       </c>
@@ -2901,7 +2926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B71" s="11">
         <v>67</v>
       </c>
@@ -2921,7 +2946,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B72" s="11">
         <v>68</v>
       </c>
@@ -2941,7 +2966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -2961,7 +2986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -2981,7 +3006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3001,7 +3026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3021,7 +3046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B77" s="11">
         <v>73</v>
       </c>
@@ -3041,7 +3066,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B78" s="11">
         <v>74</v>
       </c>
@@ -3061,7 +3086,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B79" s="11">
         <v>75</v>
       </c>
@@ -3081,7 +3106,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3102,7 +3127,7 @@
       </c>
       <c r="H80" s="22"/>
     </row>
-    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3123,7 +3148,7 @@
       </c>
       <c r="H81" s="22"/>
     </row>
-    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3144,7 +3169,7 @@
       </c>
       <c r="H82" s="22"/>
     </row>
-    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3165,7 +3190,7 @@
       </c>
       <c r="H83" s="22"/>
     </row>
-    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="16">
         <v>80</v>
       </c>
@@ -3188,7 +3213,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16">
         <v>81</v>
       </c>
@@ -3211,7 +3236,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="16">
         <v>82</v>
       </c>
@@ -3234,7 +3259,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="16">
         <v>83</v>
       </c>
@@ -3257,7 +3282,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="16">
         <v>84</v>
       </c>
@@ -3280,7 +3305,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3301,7 +3326,7 @@
       </c>
       <c r="H89" s="22"/>
     </row>
-    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3322,7 +3347,7 @@
       </c>
       <c r="H90" s="22"/>
     </row>
-    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3343,7 +3368,7 @@
       </c>
       <c r="H91" s="22"/>
     </row>
-    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3364,7 +3389,7 @@
       </c>
       <c r="H92" s="19"/>
     </row>
-    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3385,7 +3410,7 @@
       </c>
       <c r="H93" s="22"/>
     </row>
-    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3406,7 +3431,7 @@
       </c>
       <c r="H94" s="22"/>
     </row>
-    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3427,7 +3452,7 @@
       </c>
       <c r="H95" s="22"/>
     </row>
-    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3448,7 +3473,7 @@
       </c>
       <c r="H96" s="22"/>
     </row>
-    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3469,7 +3494,7 @@
       </c>
       <c r="H97" s="22"/>
     </row>
-    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3490,7 +3515,7 @@
       </c>
       <c r="H98" s="22"/>
     </row>
-    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -3511,7 +3536,7 @@
       </c>
       <c r="H99" s="22"/>
     </row>
-    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -3532,7 +3557,7 @@
       </c>
       <c r="H100" s="22"/>
     </row>
-    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -3553,7 +3578,7 @@
       </c>
       <c r="H101" s="22"/>
     </row>
-    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -3574,7 +3599,7 @@
       </c>
       <c r="H102" s="22"/>
     </row>
-    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -3595,7 +3620,7 @@
       </c>
       <c r="H103" s="22"/>
     </row>
-    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FB938A-5325-41D1-BC57-0EC6965EFB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B45B69B-6C81-4D90-B647-E8AA521043D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="259">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -886,6 +886,14 @@
   </si>
   <si>
     <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1430,21 +1438,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:I104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="254.625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="254.6328125" style="19" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1458,7 +1466,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="18"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1470,7 +1478,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="19"/>
     </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1494,7 +1502,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1520,7 +1528,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>1</v>
       </c>
@@ -1543,7 +1551,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="11">
         <v>2</v>
@@ -1567,7 +1575,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -1590,7 +1598,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -1613,7 +1621,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -1636,7 +1644,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -1659,7 +1667,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1680,7 +1688,7 @@
       </c>
       <c r="H11" s="25"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -1703,7 +1711,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="H13" s="25"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -1743,8 +1751,11 @@
       <c r="G14" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H14" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="11">
         <v>11</v>
       </c>
@@ -1763,8 +1774,11 @@
       <c r="G15" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H15" s="21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -1784,7 +1798,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="11">
         <v>13</v>
       </c>
@@ -1804,7 +1818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -1824,7 +1838,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -1844,7 +1858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="11">
         <v>16</v>
       </c>
@@ -1867,7 +1881,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="11">
         <v>17</v>
       </c>
@@ -1890,7 +1904,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="11">
         <v>18</v>
       </c>
@@ -1913,7 +1927,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -1933,7 +1947,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -1953,7 +1967,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -1973,7 +1987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -1993,7 +2007,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="11">
         <v>23</v>
       </c>
@@ -2013,7 +2027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="11">
         <v>24</v>
       </c>
@@ -2033,7 +2047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="11">
         <v>25</v>
       </c>
@@ -2053,7 +2067,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="11">
         <v>26</v>
       </c>
@@ -2073,7 +2087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2093,7 +2107,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2113,7 +2127,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2133,7 +2147,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2153,7 +2167,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2173,7 +2187,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2193,7 +2207,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2213,7 +2227,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2233,7 +2247,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="16">
         <v>35</v>
       </c>
@@ -2256,7 +2270,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="16">
         <v>36</v>
       </c>
@@ -2279,7 +2293,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="16">
         <v>37</v>
       </c>
@@ -2302,7 +2316,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16">
         <v>38</v>
       </c>
@@ -2325,7 +2339,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="16">
         <v>39</v>
       </c>
@@ -2348,7 +2362,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="16">
         <v>40</v>
       </c>
@@ -2371,7 +2385,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="16">
         <v>41</v>
       </c>
@@ -2394,7 +2408,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="16">
         <v>42</v>
       </c>
@@ -2417,7 +2431,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="16">
         <v>43</v>
       </c>
@@ -2440,7 +2454,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="16">
         <v>44</v>
       </c>
@@ -2463,7 +2477,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="16">
         <v>45</v>
       </c>
@@ -2486,7 +2500,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="16">
         <v>46</v>
       </c>
@@ -2509,7 +2523,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="16">
         <v>47</v>
       </c>
@@ -2532,7 +2546,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="16">
         <v>48</v>
       </c>
@@ -2555,7 +2569,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="16">
         <v>49</v>
       </c>
@@ -2578,7 +2592,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="11">
         <v>50</v>
       </c>
@@ -2598,7 +2612,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2619,7 +2633,7 @@
       </c>
       <c r="H55" s="22"/>
     </row>
-    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2640,7 +2654,7 @@
       </c>
       <c r="H56" s="22"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -2660,7 +2674,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="11">
         <v>54</v>
       </c>
@@ -2680,7 +2694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="11">
         <v>55</v>
       </c>
@@ -2700,7 +2714,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="11">
         <v>56</v>
       </c>
@@ -2720,7 +2734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="11">
         <v>57</v>
       </c>
@@ -2740,7 +2754,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="11">
         <v>58</v>
       </c>
@@ -2760,7 +2774,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" s="11">
         <v>59</v>
       </c>
@@ -2780,7 +2794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="11">
         <v>60</v>
       </c>
@@ -2800,7 +2814,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="11">
         <v>61</v>
       </c>
@@ -2820,7 +2834,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="16">
         <v>62</v>
       </c>
@@ -2846,7 +2860,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="11">
         <v>63</v>
       </c>
@@ -2866,7 +2880,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="11">
         <v>64</v>
       </c>
@@ -2886,7 +2900,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="11">
         <v>65</v>
       </c>
@@ -2906,7 +2920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="11">
         <v>66</v>
       </c>
@@ -2926,7 +2940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="11">
         <v>67</v>
       </c>
@@ -2946,7 +2960,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="11">
         <v>68</v>
       </c>
@@ -2966,7 +2980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -2986,7 +3000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3006,7 +3020,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3026,7 +3040,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3046,7 +3060,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="11">
         <v>73</v>
       </c>
@@ -3066,7 +3080,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="11">
         <v>74</v>
       </c>
@@ -3086,7 +3100,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="11">
         <v>75</v>
       </c>
@@ -3106,7 +3120,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3127,7 +3141,7 @@
       </c>
       <c r="H80" s="22"/>
     </row>
-    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3148,7 +3162,7 @@
       </c>
       <c r="H81" s="22"/>
     </row>
-    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3169,7 +3183,7 @@
       </c>
       <c r="H82" s="22"/>
     </row>
-    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3190,7 +3204,7 @@
       </c>
       <c r="H83" s="22"/>
     </row>
-    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="16">
         <v>80</v>
       </c>
@@ -3213,7 +3227,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="16">
         <v>81</v>
       </c>
@@ -3236,7 +3250,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="16">
         <v>82</v>
       </c>
@@ -3259,7 +3273,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="16">
         <v>83</v>
       </c>
@@ -3282,7 +3296,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="16">
         <v>84</v>
       </c>
@@ -3305,7 +3319,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3326,7 +3340,7 @@
       </c>
       <c r="H89" s="22"/>
     </row>
-    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3347,7 +3361,7 @@
       </c>
       <c r="H90" s="22"/>
     </row>
-    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3368,7 +3382,7 @@
       </c>
       <c r="H91" s="22"/>
     </row>
-    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3389,7 +3403,7 @@
       </c>
       <c r="H92" s="19"/>
     </row>
-    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3410,7 +3424,7 @@
       </c>
       <c r="H93" s="22"/>
     </row>
-    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3431,7 +3445,7 @@
       </c>
       <c r="H94" s="22"/>
     </row>
-    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3452,7 +3466,7 @@
       </c>
       <c r="H95" s="22"/>
     </row>
-    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3473,7 +3487,7 @@
       </c>
       <c r="H96" s="22"/>
     </row>
-    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3494,7 +3508,7 @@
       </c>
       <c r="H97" s="22"/>
     </row>
-    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3515,7 +3529,7 @@
       </c>
       <c r="H98" s="22"/>
     </row>
-    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -3536,7 +3550,7 @@
       </c>
       <c r="H99" s="22"/>
     </row>
-    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -3557,7 +3571,7 @@
       </c>
       <c r="H100" s="22"/>
     </row>
-    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -3578,7 +3592,7 @@
       </c>
       <c r="H101" s="22"/>
     </row>
-    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -3599,7 +3613,7 @@
       </c>
       <c r="H102" s="22"/>
     </row>
-    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -3620,7 +3634,7 @@
       </c>
       <c r="H103" s="22"/>
     </row>
-    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B45B69B-6C81-4D90-B647-E8AA521043D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA74602-FD73-410C-885E-9258469C55E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="262">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -889,11 +889,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1050,7 +1062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1085,14 +1097,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1126,6 +1132,24 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1438,21 +1462,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:I104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="254.6328125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="254.625" style="17" customWidth="1"/>
+    <col min="9" max="9" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1464,9 +1488,9 @@
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1476,9 +1500,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1498,11 +1522,11 @@
         <v>12</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1524,150 +1548,155 @@
       <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="12">
+    <row r="5" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="26">
         <v>4</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="26">
         <v>1</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="11">
-        <v>2</v>
-      </c>
-      <c r="C6" s="11" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28">
+        <v>2</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="11">
-        <v>3</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="28">
+        <v>3</v>
+      </c>
+      <c r="F6" s="28">
         <v>1</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
-        <v>3</v>
-      </c>
-      <c r="C7" s="11" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7" s="29"/>
+      <c r="B7" s="28">
+        <v>3</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11">
-        <v>3</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="E7" s="28">
+        <v>3</v>
+      </c>
+      <c r="F7" s="26">
         <v>1</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="19" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A8" s="29"/>
+      <c r="B8" s="28">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11">
-        <v>2</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="E8" s="28">
+        <v>2</v>
+      </c>
+      <c r="F8" s="28">
         <v>1</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="19" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A9" s="29"/>
+      <c r="B9" s="28">
         <v>5</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="11">
-        <v>2</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="E9" s="28">
+        <v>2</v>
+      </c>
+      <c r="F9" s="26">
         <v>1</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A10" s="29"/>
+      <c r="B10" s="28">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="11">
-        <v>2</v>
-      </c>
-      <c r="F10" s="11">
+      <c r="E10" s="28">
+        <v>2</v>
+      </c>
+      <c r="F10" s="28">
         <v>1</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="19" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1680,38 +1709,38 @@
       <c r="E11" s="9">
         <v>2</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <v>1</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="28">
         <v>8</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="11">
-        <v>2</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="E12" s="28">
+        <v>2</v>
+      </c>
+      <c r="F12" s="28">
         <v>1</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="19" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1724,61 +1753,61 @@
       <c r="E13" s="9">
         <v>2</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <v>1</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="11">
+      <c r="H13" s="23"/>
+    </row>
+    <row r="14" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="28">
         <v>10</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="11">
-        <v>2</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2</v>
-      </c>
-      <c r="G14" s="11" t="s">
+      <c r="E14" s="28">
+        <v>2</v>
+      </c>
+      <c r="F14" s="28">
+        <v>2</v>
+      </c>
+      <c r="G14" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="21" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="11">
+      <c r="H14" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="28">
         <v>11</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="11">
-        <v>3</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2</v>
-      </c>
-      <c r="G15" s="11" t="s">
+      <c r="E15" s="28">
+        <v>3</v>
+      </c>
+      <c r="F15" s="28">
+        <v>2</v>
+      </c>
+      <c r="G15" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -1798,27 +1827,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11">
+    <row r="17" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="28">
         <v>13</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="11">
-        <v>2</v>
-      </c>
-      <c r="F17" s="11">
-        <v>2</v>
-      </c>
-      <c r="G17" s="11" t="s">
+      <c r="E17" s="28">
+        <v>2</v>
+      </c>
+      <c r="F17" s="28">
+        <v>2</v>
+      </c>
+      <c r="G17" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="24" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -1838,7 +1870,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -1858,76 +1890,76 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11">
+    <row r="20" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="28">
         <v>16</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="11">
-        <v>2</v>
-      </c>
-      <c r="F20" s="11">
-        <v>2</v>
-      </c>
-      <c r="G20" s="11" t="s">
+      <c r="E20" s="28">
+        <v>2</v>
+      </c>
+      <c r="F20" s="28">
+        <v>2</v>
+      </c>
+      <c r="G20" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="19" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11">
+    <row r="21" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="28">
         <v>17</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="11">
-        <v>2</v>
-      </c>
-      <c r="F21" s="11">
+      <c r="E21" s="28">
+        <v>2</v>
+      </c>
+      <c r="F21" s="28">
         <v>4</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="19" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="11">
+    <row r="22" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="28">
         <v>18</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="11">
-        <v>3</v>
-      </c>
-      <c r="F22" s="11">
-        <v>2</v>
-      </c>
-      <c r="G22" s="11" t="s">
+      <c r="E22" s="28">
+        <v>3</v>
+      </c>
+      <c r="F22" s="28">
+        <v>2</v>
+      </c>
+      <c r="G22" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="19" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -1947,7 +1979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -1967,7 +1999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -1987,7 +2019,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2007,47 +2039,53 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="11">
+    <row r="27" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="28">
         <v>23</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="11">
-        <v>2</v>
-      </c>
-      <c r="F27" s="11">
-        <v>2</v>
-      </c>
-      <c r="G27" s="11" t="s">
+      <c r="E27" s="28">
+        <v>2</v>
+      </c>
+      <c r="F27" s="28">
+        <v>2</v>
+      </c>
+      <c r="G27" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="11">
+      <c r="H27" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="28">
         <v>24</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="11">
-        <v>3</v>
-      </c>
-      <c r="F28" s="11">
-        <v>2</v>
-      </c>
-      <c r="G28" s="11" t="s">
+      <c r="E28" s="28">
+        <v>3</v>
+      </c>
+      <c r="F28" s="28">
+        <v>2</v>
+      </c>
+      <c r="G28" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H28" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="11">
         <v>25</v>
       </c>
@@ -2067,7 +2105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="11">
         <v>26</v>
       </c>
@@ -2087,7 +2125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2107,7 +2145,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2127,7 +2165,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2147,7 +2185,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2167,7 +2205,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2187,7 +2225,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2207,7 +2245,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2227,7 +2265,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2247,352 +2285,352 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="2:8" s="17" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="16">
+    <row r="39" spans="2:8" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="14">
         <v>35</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E39" s="16">
-        <v>2</v>
-      </c>
-      <c r="F39" s="16">
-        <v>2</v>
-      </c>
-      <c r="G39" s="16" t="s">
+      <c r="E39" s="14">
+        <v>2</v>
+      </c>
+      <c r="F39" s="14">
+        <v>2</v>
+      </c>
+      <c r="G39" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H39" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="16">
+    <row r="40" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="14">
         <v>36</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="16">
-        <v>2</v>
-      </c>
-      <c r="F40" s="16">
-        <v>2</v>
-      </c>
-      <c r="G40" s="16" t="s">
+      <c r="E40" s="14">
+        <v>2</v>
+      </c>
+      <c r="F40" s="14">
+        <v>2</v>
+      </c>
+      <c r="G40" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="21" t="s">
+      <c r="H40" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="16">
+    <row r="41" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="14">
         <v>37</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E41" s="16">
-        <v>2</v>
-      </c>
-      <c r="F41" s="16">
-        <v>2</v>
-      </c>
-      <c r="G41" s="16" t="s">
+      <c r="E41" s="14">
+        <v>2</v>
+      </c>
+      <c r="F41" s="14">
+        <v>2</v>
+      </c>
+      <c r="G41" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="H41" s="19" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="42" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="16">
+    <row r="42" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="14">
         <v>38</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="16">
-        <v>2</v>
-      </c>
-      <c r="F42" s="16">
-        <v>2</v>
-      </c>
-      <c r="G42" s="16" t="s">
+      <c r="E42" s="14">
+        <v>2</v>
+      </c>
+      <c r="F42" s="14">
+        <v>2</v>
+      </c>
+      <c r="G42" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="21" t="s">
+      <c r="H42" s="19" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="16">
+    <row r="43" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="14">
         <v>39</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E43" s="16">
-        <v>2</v>
-      </c>
-      <c r="F43" s="16">
-        <v>2</v>
-      </c>
-      <c r="G43" s="16" t="s">
+      <c r="E43" s="14">
+        <v>2</v>
+      </c>
+      <c r="F43" s="14">
+        <v>2</v>
+      </c>
+      <c r="G43" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="21" t="s">
+      <c r="H43" s="19" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="16">
+    <row r="44" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="14">
         <v>40</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="16">
-        <v>3</v>
-      </c>
-      <c r="F44" s="16">
-        <v>2</v>
-      </c>
-      <c r="G44" s="16" t="s">
+      <c r="E44" s="14">
+        <v>3</v>
+      </c>
+      <c r="F44" s="14">
+        <v>2</v>
+      </c>
+      <c r="G44" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H44" s="19" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="16">
+    <row r="45" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="14">
         <v>41</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="14">
         <v>4</v>
       </c>
-      <c r="F45" s="16">
-        <v>2</v>
-      </c>
-      <c r="G45" s="16" t="s">
+      <c r="F45" s="14">
+        <v>2</v>
+      </c>
+      <c r="G45" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="19" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="16">
+    <row r="46" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B46" s="14">
         <v>42</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="16">
-        <v>3</v>
-      </c>
-      <c r="F46" s="16">
-        <v>2</v>
-      </c>
-      <c r="G46" s="16" t="s">
+      <c r="E46" s="14">
+        <v>3</v>
+      </c>
+      <c r="F46" s="14">
+        <v>2</v>
+      </c>
+      <c r="G46" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H46" s="21" t="s">
+      <c r="H46" s="19" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="16">
+    <row r="47" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="14">
         <v>43</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="16">
-        <v>3</v>
-      </c>
-      <c r="F47" s="16">
-        <v>2</v>
-      </c>
-      <c r="G47" s="16" t="s">
+      <c r="E47" s="14">
+        <v>3</v>
+      </c>
+      <c r="F47" s="14">
+        <v>2</v>
+      </c>
+      <c r="G47" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="21" t="s">
+      <c r="H47" s="19" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="48" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="16">
+    <row r="48" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="14">
         <v>44</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="16">
-        <v>3</v>
-      </c>
-      <c r="F48" s="16">
-        <v>2</v>
-      </c>
-      <c r="G48" s="16" t="s">
+      <c r="E48" s="14">
+        <v>3</v>
+      </c>
+      <c r="F48" s="14">
+        <v>2</v>
+      </c>
+      <c r="G48" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="21" t="s">
+      <c r="H48" s="19" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="16">
+    <row r="49" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="14">
         <v>45</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E49" s="16">
-        <v>3</v>
-      </c>
-      <c r="F49" s="16">
-        <v>2</v>
-      </c>
-      <c r="G49" s="16" t="s">
+      <c r="E49" s="14">
+        <v>3</v>
+      </c>
+      <c r="F49" s="14">
+        <v>2</v>
+      </c>
+      <c r="G49" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="H49" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="50" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="16">
+    <row r="50" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="14">
         <v>46</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="E50" s="16">
-        <v>3</v>
-      </c>
-      <c r="F50" s="16">
-        <v>2</v>
-      </c>
-      <c r="G50" s="16" t="s">
+      <c r="E50" s="14">
+        <v>3</v>
+      </c>
+      <c r="F50" s="14">
+        <v>2</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="21" t="s">
+      <c r="H50" s="19" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="16">
+    <row r="51" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="14">
         <v>47</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E51" s="16">
-        <v>3</v>
-      </c>
-      <c r="F51" s="16">
-        <v>2</v>
-      </c>
-      <c r="G51" s="16" t="s">
+      <c r="E51" s="14">
+        <v>3</v>
+      </c>
+      <c r="F51" s="14">
+        <v>2</v>
+      </c>
+      <c r="G51" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H51" s="21" t="s">
+      <c r="H51" s="19" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="16">
+    <row r="52" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="14">
         <v>48</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E52" s="16">
-        <v>3</v>
-      </c>
-      <c r="F52" s="16">
-        <v>2</v>
-      </c>
-      <c r="G52" s="16" t="s">
+      <c r="E52" s="14">
+        <v>3</v>
+      </c>
+      <c r="F52" s="14">
+        <v>2</v>
+      </c>
+      <c r="G52" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="19" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="16">
+    <row r="53" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="14">
         <v>49</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="14">
         <v>4</v>
       </c>
-      <c r="F53" s="16">
-        <v>2</v>
-      </c>
-      <c r="G53" s="16" t="s">
+      <c r="F53" s="14">
+        <v>2</v>
+      </c>
+      <c r="G53" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="19" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="11">
         <v>50</v>
       </c>
@@ -2605,14 +2643,14 @@
       <c r="E54" s="11">
         <v>3</v>
       </c>
-      <c r="F54" s="15">
+      <c r="F54" s="13">
         <v>2</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2625,15 +2663,15 @@
       <c r="E55" s="9">
         <v>2</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="13">
         <v>2</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H55" s="22"/>
-    </row>
-    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="20"/>
+    </row>
+    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2646,15 +2684,15 @@
       <c r="E56" s="9">
         <v>2</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="13">
         <v>2</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H56" s="22"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H56" s="20"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -2674,7 +2712,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B58" s="11">
         <v>54</v>
       </c>
@@ -2694,7 +2732,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B59" s="11">
         <v>55</v>
       </c>
@@ -2714,7 +2752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B60" s="11">
         <v>56</v>
       </c>
@@ -2734,7 +2772,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B61" s="11">
         <v>57</v>
       </c>
@@ -2754,7 +2792,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B62" s="11">
         <v>58</v>
       </c>
@@ -2774,7 +2812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B63" s="11">
         <v>59</v>
       </c>
@@ -2794,7 +2832,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B64" s="11">
         <v>60</v>
       </c>
@@ -2814,7 +2852,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B65" s="11">
         <v>61</v>
       </c>
@@ -2834,33 +2872,33 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="16">
+    <row r="66" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B66" s="14">
         <v>62</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="14">
         <v>4</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="14">
         <v>4</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H66" s="21" t="s">
+      <c r="H66" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="I66" s="17" t="s">
+      <c r="I66" s="15" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B67" s="11">
         <v>63</v>
       </c>
@@ -2880,7 +2918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B68" s="11">
         <v>64</v>
       </c>
@@ -2900,7 +2938,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B69" s="11">
         <v>65</v>
       </c>
@@ -2920,7 +2958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B70" s="11">
         <v>66</v>
       </c>
@@ -2940,7 +2978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B71" s="11">
         <v>67</v>
       </c>
@@ -2960,7 +2998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B72" s="11">
         <v>68</v>
       </c>
@@ -2980,7 +3018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3000,7 +3038,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3020,7 +3058,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3040,7 +3078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3060,7 +3098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B77" s="11">
         <v>73</v>
       </c>
@@ -3080,7 +3118,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B78" s="11">
         <v>74</v>
       </c>
@@ -3100,7 +3138,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B79" s="11">
         <v>75</v>
       </c>
@@ -3120,7 +3158,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3139,9 +3177,9 @@
       <c r="G80" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H80" s="22"/>
-    </row>
-    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3160,9 +3198,9 @@
       <c r="G81" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H81" s="22"/>
-    </row>
-    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H81" s="20"/>
+    </row>
+    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3181,9 +3219,9 @@
       <c r="G82" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H82" s="22"/>
-    </row>
-    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3202,124 +3240,124 @@
       <c r="G83" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="H83" s="22"/>
-    </row>
-    <row r="84" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="16">
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B84" s="14">
         <v>80</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D84" s="16" t="s">
+      <c r="D84" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E84" s="16">
-        <v>2</v>
-      </c>
-      <c r="F84" s="17" t="s">
+      <c r="E84" s="14">
+        <v>2</v>
+      </c>
+      <c r="F84" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="G84" s="16" t="s">
+      <c r="G84" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H84" s="21" t="s">
+      <c r="H84" s="19" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="85" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="16">
+    <row r="85" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B85" s="14">
         <v>81</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D85" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E85" s="16">
-        <v>2</v>
-      </c>
-      <c r="F85" s="17" t="s">
+      <c r="E85" s="14">
+        <v>2</v>
+      </c>
+      <c r="F85" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H85" s="21" t="s">
+      <c r="H85" s="19" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="16">
+    <row r="86" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B86" s="14">
         <v>82</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C86" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="16">
-        <v>2</v>
-      </c>
-      <c r="F86" s="17" t="s">
+      <c r="E86" s="14">
+        <v>2</v>
+      </c>
+      <c r="F86" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H86" s="21" t="s">
+      <c r="H86" s="19" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="87" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="16">
+    <row r="87" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B87" s="14">
         <v>83</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E87" s="16">
-        <v>2</v>
-      </c>
-      <c r="F87" s="17" t="s">
+      <c r="E87" s="14">
+        <v>2</v>
+      </c>
+      <c r="F87" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G87" s="16" t="s">
+      <c r="G87" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H87" s="21" t="s">
+      <c r="H87" s="19" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="88" spans="2:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="16">
+    <row r="88" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B88" s="14">
         <v>84</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E88" s="16">
-        <v>2</v>
-      </c>
-      <c r="F88" s="17" t="s">
+      <c r="E88" s="14">
+        <v>2</v>
+      </c>
+      <c r="F88" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G88" s="16" t="s">
+      <c r="G88" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H88" s="21" t="s">
+      <c r="H88" s="19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3338,9 +3376,9 @@
       <c r="G89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H89" s="22"/>
-    </row>
-    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H89" s="20"/>
+    </row>
+    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3359,9 +3397,9 @@
       <c r="G90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H90" s="22"/>
-    </row>
-    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H90" s="20"/>
+    </row>
+    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3380,9 +3418,9 @@
       <c r="G91" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H91" s="22"/>
-    </row>
-    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H91" s="20"/>
+    </row>
+    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3401,9 +3439,9 @@
       <c r="G92" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H92" s="19"/>
-    </row>
-    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H92" s="17"/>
+    </row>
+    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3422,9 +3460,9 @@
       <c r="G93" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H93" s="22"/>
-    </row>
-    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H93" s="20"/>
+    </row>
+    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3443,9 +3481,9 @@
       <c r="G94" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H94" s="22"/>
-    </row>
-    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H94" s="20"/>
+    </row>
+    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3464,9 +3502,9 @@
       <c r="G95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H95" s="22"/>
-    </row>
-    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H95" s="20"/>
+    </row>
+    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3485,9 +3523,9 @@
       <c r="G96" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H96" s="22"/>
-    </row>
-    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H96" s="20"/>
+    </row>
+    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3506,9 +3544,9 @@
       <c r="G97" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H97" s="22"/>
-    </row>
-    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H97" s="20"/>
+    </row>
+    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3527,9 +3565,9 @@
       <c r="G98" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H98" s="22"/>
-    </row>
-    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H98" s="20"/>
+    </row>
+    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -3548,9 +3586,9 @@
       <c r="G99" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H99" s="22"/>
-    </row>
-    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H99" s="20"/>
+    </row>
+    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -3569,9 +3607,9 @@
       <c r="G100" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H100" s="22"/>
-    </row>
-    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H100" s="20"/>
+    </row>
+    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -3590,9 +3628,9 @@
       <c r="G101" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H101" s="22"/>
-    </row>
-    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H101" s="20"/>
+    </row>
+    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -3611,9 +3649,9 @@
       <c r="G102" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H102" s="22"/>
-    </row>
-    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H102" s="20"/>
+    </row>
+    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -3632,9 +3670,9 @@
       <c r="G103" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="H103" s="22"/>
-    </row>
-    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H103" s="20"/>
+    </row>
+    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>
@@ -3653,7 +3691,7 @@
       <c r="G104" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="H104" s="22"/>
+      <c r="H104" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA74602-FD73-410C-885E-9258469C55E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05D21E5-6498-47C4-AC27-DF910A14A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="264">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -906,6 +906,14 @@
   </si>
   <si>
     <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}, {class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }},]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100,, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2898,44 +2906,50 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B67" s="11">
+    <row r="67" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B67" s="28">
         <v>63</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="28">
         <v>4</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="28">
         <v>4</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="28" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B68" s="11">
+      <c r="H67" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B68" s="28">
         <v>64</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="28">
         <v>4</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="28">
         <v>4</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="28" t="s">
         <v>50</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05D21E5-6498-47C4-AC27-DF910A14A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B59AF0-0399-42C6-992B-244C2C1D756D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="280">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,726 +194,795 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>伏兵成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>计略</t>
+  </si>
+  <si>
+    <t>攻城</t>
+  </si>
+  <si>
+    <t>攻击据点、设施、建筑物时施展会心一击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掎角</t>
+  </si>
+  <si>
+    <t>施展齐攻时，让对方陷入混乱</t>
+  </si>
+  <si>
+    <t>捕缚</t>
+  </si>
+  <si>
+    <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
+  </si>
+  <si>
+    <t>精妙</t>
+  </si>
+  <si>
+    <t>击破敌方部队时所获得的技巧点数增为２倍</t>
+  </si>
+  <si>
+    <t>掠夺</t>
+  </si>
+  <si>
+    <t>击破敌方部队时，有机会夺取敌将的道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻心</t>
+  </si>
+  <si>
+    <t>攻击时可将敌方部队的一部分士兵吸收到自军部队中</t>
+  </si>
+  <si>
+    <t>驱逐</t>
+  </si>
+  <si>
+    <t>施展一般攻击时会心一击</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>使井阑、投石的射程增加１区格</t>
+  </si>
+  <si>
+    <t>未研究技巧「骑射」时也可施展骑射；骑射可施展会心一击</t>
+  </si>
+  <si>
+    <t>辅佐</t>
+  </si>
+  <si>
+    <t>即使没建立人际关系（厌恶除外）也可获得支援攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不屈</t>
+  </si>
+  <si>
+    <t>若在部队的士兵不多时被攻击，不会受到损伤</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>金刚</t>
+  </si>
+  <si>
+    <t>在敌方攻击力微弱时被攻击的话，不会受到损伤</t>
+  </si>
+  <si>
+    <t>铁壁</t>
+  </si>
+  <si>
+    <t>就算被一齐攻击，也会视之为一般攻击</t>
+  </si>
+  <si>
+    <t>怒发</t>
+  </si>
+  <si>
+    <t>遭受敌方部队的战法攻击时，气力就会回复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤甲</t>
+  </si>
+  <si>
+    <t>火以外的攻击损伤减半，但火攻的损伤将增为２倍</t>
+  </si>
+  <si>
+    <t>强运</t>
+  </si>
+  <si>
+    <t>不会战死、被俘、负伤</t>
+  </si>
+  <si>
+    <t>血路</t>
+  </si>
+  <si>
+    <t>就算部队溃灭，同部队的武将也不会被俘虏</t>
+  </si>
+  <si>
+    <t>枪将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展枪兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>戟将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展戟兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>弓将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展弩兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>骑将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展骑兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>水将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展水军战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>勇将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展全战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>神将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展一般攻击及战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>斗神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵战法与戟兵战法施展成功时会心一击</t>
+  </si>
+  <si>
+    <t>枪兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>戟神</t>
+  </si>
+  <si>
+    <t>戟兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>弓神</t>
+  </si>
+  <si>
+    <t>弩兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>骑神</t>
+  </si>
+  <si>
+    <t>骑兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>工神</t>
+  </si>
+  <si>
+    <t>兵器战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>水神</t>
+  </si>
+  <si>
+    <t>水军战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>霸王</t>
+  </si>
+  <si>
+    <t>全战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>疾驰</t>
+  </si>
+  <si>
+    <t>对攻击力比自部队低的敌方部队施展骑兵战法成功时，必使其陷入混乱</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>可于森林使用弩兵战法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猛者</t>
+  </si>
+  <si>
+    <t>以战法让敌方部队移动区格时，可让敌将负伤</t>
+  </si>
+  <si>
+    <t>护卫</t>
+  </si>
+  <si>
+    <t>同部队的武将不会战死、负伤</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「火计」时必定会成功</t>
+  </si>
+  <si>
+    <t>言毒</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「伪报」时，必定会成功</t>
+  </si>
+  <si>
+    <t>机智</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「扰乱」时，必定会成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诡计</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「内讧」时，必定会成功</t>
+  </si>
+  <si>
+    <t>虚实</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展全部队计略时，必定会成功</t>
+  </si>
+  <si>
+    <t>妙计</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略成功时会心一击</t>
+  </si>
+  <si>
+    <t>秘计</t>
+  </si>
+  <si>
+    <t>对智力比自己高的敌方部队施展部队计略成功时会心一击</t>
+  </si>
+  <si>
+    <t>看破</t>
+  </si>
+  <si>
+    <t>必定可识破智力比自己低的敌方部队所施展部队计略</t>
+  </si>
+  <si>
+    <t>洞察</t>
+  </si>
+  <si>
+    <t>火神</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展火计时必会成功；于全火攻有所优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神算</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展计略必会成功；于全计略有所优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百出</t>
+  </si>
+  <si>
+    <t>部队计略的消费气力减少</t>
+  </si>
+  <si>
+    <t>鬼谋</t>
+  </si>
+  <si>
+    <t>增广２区格可施展部队计略的范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环</t>
+  </si>
+  <si>
+    <t>部队计略成功时，与对象部队邻接的部队也会遭受计略波及</t>
+  </si>
+  <si>
+    <t>部队计略成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>反计</t>
+  </si>
+  <si>
+    <t>若识破部队计略，就可对其施展同样的计略</t>
+  </si>
+  <si>
+    <t>奇谋</t>
+  </si>
+  <si>
+    <t>妖术</t>
+  </si>
+  <si>
+    <t>可施展部队计略的「妖术」</t>
+  </si>
+  <si>
+    <t>鬼门</t>
+  </si>
+  <si>
+    <t>可施展部队计略的「妖术、落雷」</t>
+  </si>
+  <si>
+    <t>可防止遭受部队计略「伪报」</t>
+  </si>
+  <si>
+    <t>补助</t>
+  </si>
+  <si>
+    <t>沉着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可防止遭受部队计略「扰乱」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可防止遭受部队计略的「伪报、扰乱」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奏乐</t>
+  </si>
+  <si>
+    <t>每回合回复自军部队的气力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诗想</t>
+  </si>
+  <si>
+    <t>军乐台的回复气力效果增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筑城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>军事设施建设的耐久上升量增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屯田</t>
+  </si>
+  <si>
+    <t>所属于关所、港口时，士兵不会消费兵粮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名声</t>
+  </si>
+  <si>
+    <t>增加征兵时的士兵数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能吏</t>
+  </si>
+  <si>
+    <t>增加生产枪、戟、弩之兵装时的产量</t>
+  </si>
+  <si>
+    <t>繁殖</t>
+  </si>
+  <si>
+    <t>增加生产军马之兵装时的产量</t>
+  </si>
+  <si>
+    <t>生产兵器之兵装时所需的生产期间减半</t>
+  </si>
+  <si>
+    <t>造船</t>
+  </si>
+  <si>
+    <t>生产舰船之兵装时所需的生产期间减半</t>
+  </si>
+  <si>
+    <t>指导</t>
+  </si>
+  <si>
+    <t>研究技巧时的费用减半</t>
+  </si>
+  <si>
+    <t>眼力</t>
+  </si>
+  <si>
+    <t>若有未发现的在野人士时执行人材探索的话，必定会发现</t>
+  </si>
+  <si>
+    <t>论客</t>
+  </si>
+  <si>
+    <t>于同盟、停战协定、交换俘虏时容易进入舌战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>富豪</t>
+  </si>
+  <si>
+    <t>每个月的所属都市的资金收入增为1.5倍</t>
+  </si>
+  <si>
+    <t>收入</t>
+  </si>
+  <si>
+    <t>米道</t>
+  </si>
+  <si>
+    <t>每季的所属都市的兵粮收入增加为1.5倍</t>
+  </si>
+  <si>
+    <t>征税</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合所属都市都会有资金收入（一次收入将减半）</t>
+  </si>
+  <si>
+    <t>征收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个月所属都市都会有兵粮的收入（一次的收入将减半）</t>
+  </si>
+  <si>
+    <t>亲乌</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「乌丸」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灾害</t>
+  </si>
+  <si>
+    <t>亲羌</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「羌族」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲越</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「山越」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲蛮</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「南蛮」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>威压</t>
+  </si>
+  <si>
+    <t>所属都市的领内不容易出现盗贼或异族的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁政</t>
+  </si>
+  <si>
+    <t>所属相同的武将之每个月的忠诚不会下降</t>
+  </si>
+  <si>
+    <t>风水</t>
+  </si>
+  <si>
+    <t>所属都市不容易出现蝗灾、瘟疫</t>
+  </si>
+  <si>
+    <t>祈愿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属都市容易出现丰收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内助</t>
+  </si>
+  <si>
+    <t>若结婚，双方的能力全部＋２</t>
+  </si>
+  <si>
+    <t>关系</t>
+  </si>
+  <si>
+    <t>u8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对部队施展部队计略成功率增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必定可识破敌方部队所施展的部队计略,反击伤害增加为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionEntities</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:150, jobIds:[6]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:200, jobIds:[8]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:200, jobIds:[12]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[10]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[11]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加了反击伤害倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aobj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5],condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, isNormal:2, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:0, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2,3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[11,12,13,14], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1},{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[1,2,3,4,5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:0}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[6]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[7]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[27], result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}, {class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateAttackBack", value:200, isDefender:1},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24,25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[22], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[24], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[25], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[28], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetSkillCost", value:1, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:2, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:1,  kinds:[13,14]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddSkill", value:2,  kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深谋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规律</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>待伏</t>
-  </si>
-  <si>
-    <t>伏兵成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>计略</t>
-  </si>
-  <si>
-    <t>攻城</t>
-  </si>
-  <si>
-    <t>攻击据点、设施、建筑物时施展会心一击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掎角</t>
-  </si>
-  <si>
-    <t>施展齐攻时，让对方陷入混乱</t>
-  </si>
-  <si>
-    <t>捕缚</t>
-  </si>
-  <si>
-    <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
-  </si>
-  <si>
-    <t>精妙</t>
-  </si>
-  <si>
-    <t>击破敌方部队时所获得的技巧点数增为２倍</t>
-  </si>
-  <si>
-    <t>掠夺</t>
-  </si>
-  <si>
-    <t>击破敌方部队时，有机会夺取敌将的道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻心</t>
-  </si>
-  <si>
-    <t>攻击时可将敌方部队的一部分士兵吸收到自军部队中</t>
-  </si>
-  <si>
-    <t>驱逐</t>
-  </si>
-  <si>
-    <t>施展一般攻击时会心一击</t>
-  </si>
-  <si>
-    <t>射程</t>
-  </si>
-  <si>
-    <t>使井阑、投石的射程增加１区格</t>
-  </si>
-  <si>
-    <t>白马</t>
-  </si>
-  <si>
-    <t>未研究技巧「骑射」时也可施展骑射；骑射可施展会心一击</t>
-  </si>
-  <si>
-    <t>辅佐</t>
-  </si>
-  <si>
-    <t>即使没建立人际关系（厌恶除外）也可获得支援攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不屈</t>
-  </si>
-  <si>
-    <t>若在部队的士兵不多时被攻击，不会受到损伤</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>金刚</t>
-  </si>
-  <si>
-    <t>在敌方攻击力微弱时被攻击的话，不会受到损伤</t>
-  </si>
-  <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>就算被一齐攻击，也会视之为一般攻击</t>
-  </si>
-  <si>
-    <t>怒发</t>
-  </si>
-  <si>
-    <t>遭受敌方部队的战法攻击时，气力就会回复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藤甲</t>
-  </si>
-  <si>
-    <t>火以外的攻击损伤减半，但火攻的损伤将增为２倍</t>
-  </si>
-  <si>
-    <t>强运</t>
-  </si>
-  <si>
-    <t>不会战死、被俘、负伤</t>
-  </si>
-  <si>
-    <t>血路</t>
-  </si>
-  <si>
-    <t>就算部队溃灭，同部队的武将也不会被俘虏</t>
-  </si>
-  <si>
-    <t>枪将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展枪兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>戟将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展戟兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>弓将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展弩兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>骑将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展骑兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>水将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展水军战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>勇将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展全战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>神将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展一般攻击及战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>斗神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪兵战法与戟兵战法施展成功时会心一击</t>
-  </si>
-  <si>
-    <t>枪兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>戟神</t>
-  </si>
-  <si>
-    <t>戟兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>弓神</t>
-  </si>
-  <si>
-    <t>弩兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>骑神</t>
-  </si>
-  <si>
-    <t>骑兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>工神</t>
-  </si>
-  <si>
-    <t>兵器战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>水神</t>
-  </si>
-  <si>
-    <t>水军战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>霸王</t>
-  </si>
-  <si>
-    <t>全战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>疾驰</t>
-  </si>
-  <si>
-    <t>对攻击力比自部队低的敌方部队施展骑兵战法成功时，必使其陷入混乱</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>可于森林使用弩兵战法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猛者</t>
-  </si>
-  <si>
-    <t>以战法让敌方部队移动区格时，可让敌将负伤</t>
-  </si>
-  <si>
-    <t>护卫</t>
-  </si>
-  <si>
-    <t>同部队的武将不会战死、负伤</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「火计」时必定会成功</t>
-  </si>
-  <si>
-    <t>言毒</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「伪报」时，必定会成功</t>
-  </si>
-  <si>
-    <t>机智</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「扰乱」时，必定会成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诡计</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「内讧」时，必定会成功</t>
-  </si>
-  <si>
-    <t>虚实</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展全部队计略时，必定会成功</t>
-  </si>
-  <si>
-    <t>妙计</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略成功时会心一击</t>
-  </si>
-  <si>
-    <t>秘计</t>
-  </si>
-  <si>
-    <t>对智力比自己高的敌方部队施展部队计略成功时会心一击</t>
-  </si>
-  <si>
-    <t>看破</t>
-  </si>
-  <si>
-    <t>必定可识破智力比自己低的敌方部队所施展部队计略</t>
-  </si>
-  <si>
-    <t>洞察</t>
-  </si>
-  <si>
-    <t>火神</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展火计时必会成功；于全火攻有所优势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神算</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展计略必会成功；于全计略有所优势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>百出</t>
-  </si>
-  <si>
-    <t>部队计略的消费气力减少</t>
-  </si>
-  <si>
-    <t>鬼谋</t>
-  </si>
-  <si>
-    <t>增广２区格可施展部队计略的范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连环</t>
-  </si>
-  <si>
-    <t>部队计略成功时，与对象部队邻接的部队也会遭受计略波及</t>
-  </si>
-  <si>
-    <t>深谋</t>
-  </si>
-  <si>
-    <t>部队计略成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>反计</t>
-  </si>
-  <si>
-    <t>若识破部队计略，就可对其施展同样的计略</t>
-  </si>
-  <si>
-    <t>奇谋</t>
-  </si>
-  <si>
-    <t>妖术</t>
-  </si>
-  <si>
-    <t>可施展部队计略的「妖术」</t>
-  </si>
-  <si>
-    <t>鬼门</t>
-  </si>
-  <si>
-    <t>可施展部队计略的「妖术、落雷」</t>
-  </si>
-  <si>
-    <t>规律</t>
-  </si>
-  <si>
-    <t>可防止遭受部队计略「伪报」</t>
-  </si>
-  <si>
-    <t>补助</t>
-  </si>
-  <si>
-    <t>沉着</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可防止遭受部队计略「扰乱」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>明镜</t>
-  </si>
-  <si>
-    <t>可防止遭受部队计略的「伪报、扰乱」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奏乐</t>
-  </si>
-  <si>
-    <t>每回合回复自军部队的气力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诗想</t>
-  </si>
-  <si>
-    <t>军乐台的回复气力效果增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>筑城</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>军事设施建设的耐久上升量增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屯田</t>
-  </si>
-  <si>
-    <t>所属于关所、港口时，士兵不会消费兵粮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名声</t>
-  </si>
-  <si>
-    <t>增加征兵时的士兵数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能吏</t>
-  </si>
-  <si>
-    <t>增加生产枪、戟、弩之兵装时的产量</t>
-  </si>
-  <si>
-    <t>繁殖</t>
-  </si>
-  <si>
-    <t>增加生产军马之兵装时的产量</t>
-  </si>
-  <si>
-    <t>生产兵器之兵装时所需的生产期间减半</t>
-  </si>
-  <si>
-    <t>造船</t>
-  </si>
-  <si>
-    <t>生产舰船之兵装时所需的生产期间减半</t>
-  </si>
-  <si>
-    <t>指导</t>
-  </si>
-  <si>
-    <t>研究技巧时的费用减半</t>
-  </si>
-  <si>
-    <t>眼力</t>
-  </si>
-  <si>
-    <t>若有未发现的在野人士时执行人材探索的话，必定会发现</t>
-  </si>
-  <si>
-    <t>论客</t>
-  </si>
-  <si>
-    <t>于同盟、停战协定、交换俘虏时容易进入舌战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>富豪</t>
-  </si>
-  <si>
-    <t>每个月的所属都市的资金收入增为1.5倍</t>
-  </si>
-  <si>
-    <t>收入</t>
-  </si>
-  <si>
-    <t>米道</t>
-  </si>
-  <si>
-    <t>每季的所属都市的兵粮收入增加为1.5倍</t>
-  </si>
-  <si>
-    <t>征税</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每回合所属都市都会有资金收入（一次收入将减半）</t>
-  </si>
-  <si>
-    <t>征收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个月所属都市都会有兵粮的收入（一次的收入将减半）</t>
-  </si>
-  <si>
-    <t>亲乌</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「乌丸」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灾害</t>
-  </si>
-  <si>
-    <t>亲羌</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「羌族」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亲越</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「山越」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亲蛮</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「南蛮」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>威压</t>
-  </si>
-  <si>
-    <t>所属都市的领内不容易出现盗贼或异族的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仁政</t>
-  </si>
-  <si>
-    <t>所属相同的武将之每个月的忠诚不会下降</t>
-  </si>
-  <si>
-    <t>风水</t>
-  </si>
-  <si>
-    <t>所属都市不容易出现蝗灾、瘟疫</t>
-  </si>
-  <si>
-    <t>祈愿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属都市容易出现丰收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内助</t>
-  </si>
-  <si>
-    <t>若结婚，双方的能力全部＋２</t>
-  </si>
-  <si>
-    <t>关系</t>
-  </si>
-  <si>
-    <t>u8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对部队施展部队计略成功率增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必定可识破敌方部队所施展的部队计略,反击伤害增加为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>actionEntities</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:150, jobIds:[6]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:200, jobIds:[8]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:200, jobIds:[12]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[10]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[11]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加了反击伤害倍率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aobj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5],condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, isNormal:2, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:0, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2,3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[11,12,13,14], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateAttackBack", value:200, isDefender:1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:1},{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[5]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[1,2,3,4,5]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:0}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[6]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[7]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[27], result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}, {class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }},]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100,, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1531,7 +1600,7 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="16" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1548,16 +1617,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.15">
@@ -1581,7 +1650,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -1605,7 +1674,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -1629,7 +1698,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -1653,7 +1722,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -1677,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -1701,7 +1770,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
@@ -1745,7 +1814,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
@@ -1789,7 +1858,7 @@
         <v>35</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -1812,7 +1881,7 @@
         <v>35</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -1855,7 +1924,7 @@
         <v>35</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.15">
@@ -1918,7 +1987,7 @@
         <v>35</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -1926,10 +1995,10 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="28" t="s">
         <v>48</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>49</v>
       </c>
       <c r="E21" s="28">
         <v>2</v>
@@ -1938,10 +2007,10 @@
         <v>4</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -1949,10 +2018,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>51</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>52</v>
       </c>
       <c r="E22" s="28">
         <v>3</v>
@@ -1964,7 +2033,7 @@
         <v>35</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.15">
@@ -1972,10 +2041,10 @@
         <v>19</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="E23" s="11">
         <v>2</v>
@@ -1992,10 +2061,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="E24" s="11">
         <v>2</v>
@@ -2012,10 +2081,10 @@
         <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="E25" s="11">
         <v>2</v>
@@ -2032,10 +2101,10 @@
         <v>22</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="E26" s="11">
         <v>2</v>
@@ -2052,10 +2121,10 @@
         <v>23</v>
       </c>
       <c r="C27" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>61</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>62</v>
       </c>
       <c r="E27" s="28">
         <v>2</v>
@@ -2067,7 +2136,7 @@
         <v>35</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2075,10 +2144,10 @@
         <v>24</v>
       </c>
       <c r="C28" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="28" t="s">
         <v>63</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>64</v>
       </c>
       <c r="E28" s="28">
         <v>3</v>
@@ -2090,47 +2159,53 @@
         <v>35</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B29" s="11">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="28">
         <v>25</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="28">
+        <v>2</v>
+      </c>
+      <c r="F29" s="28">
+        <v>2</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="28">
+        <v>26</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="11">
-        <v>2</v>
-      </c>
-      <c r="F29" s="11">
-        <v>2</v>
-      </c>
-      <c r="G29" s="11" t="s">
+      <c r="E30" s="28">
+        <v>2</v>
+      </c>
+      <c r="F30" s="28">
+        <v>2</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B30" s="11">
-        <v>26</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="11">
-        <v>2</v>
-      </c>
-      <c r="F30" s="11">
-        <v>2</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>35</v>
+      <c r="H30" s="19" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.15">
@@ -2138,10 +2213,10 @@
         <v>27</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E31" s="11">
         <v>2</v>
@@ -2158,19 +2233,19 @@
         <v>28</v>
       </c>
       <c r="C32" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="11">
+        <v>2</v>
+      </c>
+      <c r="F32" s="11">
+        <v>3</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="11">
-        <v>2</v>
-      </c>
-      <c r="F32" s="11">
-        <v>3</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.15">
@@ -2178,10 +2253,10 @@
         <v>29</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E33" s="11">
         <v>2</v>
@@ -2190,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.15">
@@ -2198,10 +2273,10 @@
         <v>30</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E34" s="11">
         <v>2</v>
@@ -2210,7 +2285,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.15">
@@ -2218,10 +2293,10 @@
         <v>31</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E35" s="11">
         <v>2</v>
@@ -2230,7 +2305,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.15">
@@ -2238,10 +2313,10 @@
         <v>32</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E36" s="11">
         <v>2</v>
@@ -2250,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.15">
@@ -2258,10 +2333,10 @@
         <v>33</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37" s="11">
         <v>4</v>
@@ -2270,7 +2345,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.15">
@@ -2278,10 +2353,10 @@
         <v>34</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E38" s="11">
         <v>2</v>
@@ -2290,7 +2365,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="2:8" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2298,10 +2373,10 @@
         <v>35</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E39" s="14">
         <v>2</v>
@@ -2313,7 +2388,7 @@
         <v>35</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2321,10 +2396,10 @@
         <v>36</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E40" s="14">
         <v>2</v>
@@ -2336,7 +2411,7 @@
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2344,10 +2419,10 @@
         <v>37</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E41" s="14">
         <v>2</v>
@@ -2359,7 +2434,7 @@
         <v>35</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2367,10 +2442,10 @@
         <v>38</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E42" s="14">
         <v>2</v>
@@ -2382,7 +2457,7 @@
         <v>35</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2390,10 +2465,10 @@
         <v>39</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E43" s="14">
         <v>2</v>
@@ -2405,7 +2480,7 @@
         <v>35</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2413,10 +2488,10 @@
         <v>40</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E44" s="14">
         <v>3</v>
@@ -2428,7 +2503,7 @@
         <v>35</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2436,10 +2511,10 @@
         <v>41</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E45" s="14">
         <v>4</v>
@@ -2451,7 +2526,7 @@
         <v>35</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2459,10 +2534,10 @@
         <v>42</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E46" s="14">
         <v>3</v>
@@ -2474,7 +2549,7 @@
         <v>35</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2482,10 +2557,10 @@
         <v>43</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E47" s="14">
         <v>3</v>
@@ -2497,7 +2572,7 @@
         <v>35</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2505,10 +2580,10 @@
         <v>44</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E48" s="14">
         <v>3</v>
@@ -2520,7 +2595,7 @@
         <v>35</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2528,10 +2603,10 @@
         <v>45</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E49" s="14">
         <v>3</v>
@@ -2543,7 +2618,7 @@
         <v>35</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2551,10 +2626,10 @@
         <v>46</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E50" s="14">
         <v>3</v>
@@ -2566,7 +2641,7 @@
         <v>35</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2574,10 +2649,10 @@
         <v>47</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E51" s="14">
         <v>3</v>
@@ -2589,7 +2664,7 @@
         <v>35</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2597,10 +2672,10 @@
         <v>48</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E52" s="14">
         <v>3</v>
@@ -2612,7 +2687,7 @@
         <v>35</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2620,10 +2695,10 @@
         <v>49</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E53" s="14">
         <v>4</v>
@@ -2635,7 +2710,7 @@
         <v>35</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2643,10 +2718,10 @@
         <v>50</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E54" s="11">
         <v>3</v>
@@ -2663,10 +2738,10 @@
         <v>51</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E55" s="9">
         <v>2</v>
@@ -2684,10 +2759,10 @@
         <v>52</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E56" s="9">
         <v>2</v>
@@ -2705,179 +2780,203 @@
         <v>53</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="11">
+        <v>2</v>
+      </c>
+      <c r="F57" s="11">
+        <v>3</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="28">
+        <v>54</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="E58" s="28">
+        <v>3</v>
+      </c>
+      <c r="F58" s="28">
+        <v>4</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B59" s="28">
+        <v>55</v>
+      </c>
+      <c r="C59" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="E57" s="11">
-        <v>2</v>
-      </c>
-      <c r="F57" s="11">
-        <v>3</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B58" s="11">
-        <v>54</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="D59" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="E58" s="11">
-        <v>3</v>
-      </c>
-      <c r="F58" s="11">
+      <c r="E59" s="28">
+        <v>3</v>
+      </c>
+      <c r="F59" s="28">
         <v>4</v>
       </c>
-      <c r="G58" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B59" s="11">
-        <v>55</v>
-      </c>
-      <c r="C59" s="11" t="s">
+      <c r="G59" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B60" s="28">
+        <v>56</v>
+      </c>
+      <c r="C60" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D60" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="11">
-        <v>3</v>
-      </c>
-      <c r="F59" s="11">
+      <c r="E60" s="28">
+        <v>3</v>
+      </c>
+      <c r="F60" s="28">
         <v>4</v>
       </c>
-      <c r="G59" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B60" s="11">
-        <v>56</v>
-      </c>
-      <c r="C60" s="11" t="s">
+      <c r="G60" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H60" s="24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B61" s="28">
+        <v>57</v>
+      </c>
+      <c r="C61" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D61" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E60" s="11">
-        <v>3</v>
-      </c>
-      <c r="F60" s="11">
+      <c r="E61" s="28">
+        <v>3</v>
+      </c>
+      <c r="F61" s="28">
         <v>4</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B61" s="11">
-        <v>57</v>
-      </c>
-      <c r="C61" s="11" t="s">
+      <c r="G61" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" s="24" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B62" s="28">
+        <v>58</v>
+      </c>
+      <c r="C62" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D62" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="E61" s="11">
-        <v>3</v>
-      </c>
-      <c r="F61" s="11">
+      <c r="E62" s="28">
         <v>4</v>
       </c>
-      <c r="G61" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B62" s="11">
-        <v>58</v>
-      </c>
-      <c r="C62" s="11" t="s">
+      <c r="F62" s="28">
+        <v>4</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B63" s="28">
+        <v>59</v>
+      </c>
+      <c r="C63" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D63" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E63" s="28">
+        <v>2</v>
+      </c>
+      <c r="F63" s="28">
         <v>4</v>
       </c>
-      <c r="F62" s="11">
+      <c r="G63" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="28">
+        <v>60</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" s="28">
+        <v>2</v>
+      </c>
+      <c r="F64" s="28">
         <v>4</v>
       </c>
-      <c r="G62" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B63" s="11">
-        <v>59</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E63" s="11">
-        <v>2</v>
-      </c>
-      <c r="F63" s="11">
+      <c r="G64" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="28">
+        <v>61</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" s="28">
+        <v>3</v>
+      </c>
+      <c r="F65" s="28">
         <v>4</v>
       </c>
-      <c r="G63" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B64" s="11">
-        <v>60</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E64" s="11">
-        <v>2</v>
-      </c>
-      <c r="F64" s="11">
-        <v>4</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B65" s="11">
-        <v>61</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E65" s="11">
-        <v>3</v>
-      </c>
-      <c r="F65" s="11">
-        <v>4</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>50</v>
+      <c r="G65" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2885,10 +2984,10 @@
         <v>62</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E66" s="14">
         <v>4</v>
@@ -2897,13 +2996,13 @@
         <v>4</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2911,10 +3010,10 @@
         <v>63</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E67" s="28">
         <v>4</v>
@@ -2923,10 +3022,10 @@
         <v>4</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2934,10 +3033,10 @@
         <v>64</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E68" s="28">
         <v>4</v>
@@ -2946,50 +3045,56 @@
         <v>4</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B69" s="11">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B69" s="28">
         <v>65</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E69" s="28">
+        <v>4</v>
+      </c>
+      <c r="F69" s="28">
+        <v>4</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" s="19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B70" s="28">
+        <v>66</v>
+      </c>
+      <c r="C70" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D70" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E70" s="28">
+        <v>3</v>
+      </c>
+      <c r="F70" s="28">
         <v>4</v>
       </c>
-      <c r="F69" s="11">
-        <v>4</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B70" s="11">
-        <v>66</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E70" s="11">
-        <v>3</v>
-      </c>
-      <c r="F70" s="11">
-        <v>4</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>50</v>
+      <c r="G70" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.15">
@@ -2997,10 +3102,10 @@
         <v>67</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E71" s="11">
         <v>3</v>
@@ -3009,27 +3114,30 @@
         <v>4</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B72" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B72" s="28">
         <v>68</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E72" s="11">
-        <v>3</v>
-      </c>
-      <c r="F72" s="11">
+      <c r="C72" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72" s="28">
+        <v>3</v>
+      </c>
+      <c r="F72" s="28">
         <v>4</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>50</v>
+      <c r="G72" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" s="19" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.15">
@@ -3037,10 +3145,10 @@
         <v>69</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E73" s="11">
         <v>3</v>
@@ -3049,7 +3157,7 @@
         <v>4</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.15">
@@ -3057,10 +3165,10 @@
         <v>70</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E74" s="11">
         <v>3</v>
@@ -3069,7 +3177,7 @@
         <v>4</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.15">
@@ -3077,10 +3185,10 @@
         <v>71</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E75" s="11">
         <v>3</v>
@@ -3089,7 +3197,7 @@
         <v>4</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.15">
@@ -3097,10 +3205,10 @@
         <v>72</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E76" s="11">
         <v>4</v>
@@ -3109,67 +3217,76 @@
         <v>4</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B77" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B77" s="28">
         <v>73</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E77" s="28">
+        <v>2</v>
+      </c>
+      <c r="F77" s="28">
+        <v>5</v>
+      </c>
+      <c r="G77" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H77" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B78" s="28">
+        <v>74</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D78" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="E78" s="28">
+        <v>2</v>
+      </c>
+      <c r="F78" s="28">
+        <v>5</v>
+      </c>
+      <c r="G78" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H78" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B79" s="28">
+        <v>75</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="D79" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="E77" s="11">
-        <v>2</v>
-      </c>
-      <c r="F77" s="11">
+      <c r="E79" s="28">
+        <v>3</v>
+      </c>
+      <c r="F79" s="28">
         <v>5</v>
       </c>
-      <c r="G77" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B78" s="11">
-        <v>74</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D78" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E78" s="11">
-        <v>2</v>
-      </c>
-      <c r="F78" s="11">
-        <v>5</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B79" s="11">
-        <v>75</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E79" s="11">
-        <v>3</v>
-      </c>
-      <c r="F79" s="11">
-        <v>5</v>
-      </c>
-      <c r="G79" s="11" t="s">
-        <v>160</v>
+      <c r="G79" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H79" s="24" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3177,10 +3294,10 @@
         <v>76</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E80" s="9">
         <v>3</v>
@@ -3189,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H80" s="20"/>
     </row>
@@ -3198,10 +3315,10 @@
         <v>77</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E81" s="9">
         <v>2</v>
@@ -3210,7 +3327,7 @@
         <v>5</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H81" s="20"/>
     </row>
@@ -3219,10 +3336,10 @@
         <v>78</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E82" s="9">
         <v>2</v>
@@ -3231,7 +3348,7 @@
         <v>5</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H82" s="20"/>
     </row>
@@ -3240,10 +3357,10 @@
         <v>79</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E83" s="9">
         <v>2</v>
@@ -3252,7 +3369,7 @@
         <v>5</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H83" s="20"/>
     </row>
@@ -3261,22 +3378,22 @@
         <v>80</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E84" s="14">
         <v>2</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G84" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3284,22 +3401,22 @@
         <v>81</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E85" s="14">
         <v>2</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G85" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3307,22 +3424,22 @@
         <v>82</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E86" s="14">
         <v>2</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G86" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3333,19 +3450,19 @@
         <v>8</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E87" s="14">
         <v>2</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G87" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3353,22 +3470,22 @@
         <v>84</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E88" s="14">
         <v>2</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G88" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3376,16 +3493,16 @@
         <v>85</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E89" s="9">
         <v>2</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>10</v>
@@ -3397,10 +3514,10 @@
         <v>86</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E90" s="9">
         <v>2</v>
@@ -3418,10 +3535,10 @@
         <v>87</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E91" s="9">
         <v>2</v>
@@ -3439,10 +3556,10 @@
         <v>88</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E92" s="9">
         <v>3</v>
@@ -3451,7 +3568,7 @@
         <v>7</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H92" s="17"/>
     </row>
@@ -3460,10 +3577,10 @@
         <v>89</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E93" s="9">
         <v>3</v>
@@ -3472,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H93" s="20"/>
     </row>
@@ -3481,10 +3598,10 @@
         <v>90</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E94" s="9">
         <v>3</v>
@@ -3493,7 +3610,7 @@
         <v>7</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H94" s="20"/>
     </row>
@@ -3502,10 +3619,10 @@
         <v>91</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E95" s="9">
         <v>3</v>
@@ -3514,7 +3631,7 @@
         <v>7</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H95" s="20"/>
     </row>
@@ -3523,10 +3640,10 @@
         <v>92</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E96" s="9">
         <v>2</v>
@@ -3535,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H96" s="20"/>
     </row>
@@ -3544,10 +3661,10 @@
         <v>93</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E97" s="9">
         <v>2</v>
@@ -3556,7 +3673,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H97" s="20"/>
     </row>
@@ -3565,10 +3682,10 @@
         <v>94</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E98" s="9">
         <v>2</v>
@@ -3577,7 +3694,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H98" s="20"/>
     </row>
@@ -3586,10 +3703,10 @@
         <v>95</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E99" s="9">
         <v>2</v>
@@ -3598,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H99" s="20"/>
     </row>
@@ -3607,10 +3724,10 @@
         <v>96</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E100" s="9">
         <v>2</v>
@@ -3619,7 +3736,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H100" s="20"/>
     </row>
@@ -3628,10 +3745,10 @@
         <v>97</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E101" s="9">
         <v>2</v>
@@ -3640,7 +3757,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H101" s="20"/>
     </row>
@@ -3649,10 +3766,10 @@
         <v>98</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E102" s="9">
         <v>2</v>
@@ -3661,7 +3778,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H102" s="20"/>
     </row>
@@ -3670,10 +3787,10 @@
         <v>99</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E103" s="9">
         <v>2</v>
@@ -3682,7 +3799,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H103" s="20"/>
     </row>
@@ -3691,10 +3808,10 @@
         <v>100</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E104" s="9">
         <v>2</v>
@@ -3703,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H104" s="20"/>
     </row>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B59AF0-0399-42C6-992B-244C2C1D756D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B99C5-31D8-4372-861D-0E496078A287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="283">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -983,6 +983,22 @@
   </si>
   <si>
     <t>待伏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
+},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
+}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hasInit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1139,7 +1155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1226,6 +1242,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1538,22 +1560,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="254.625" style="17" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1564,10 +1587,11 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="16"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G1" s="5"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1577,9 +1601,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H2" s="2"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1593,17 +1618,20 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="16" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1617,19 +1645,22 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>212</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="I4" s="18" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1641,19 +1672,22 @@
         <v>15</v>
       </c>
       <c r="E5" s="26">
+        <v>1</v>
+      </c>
+      <c r="F5" s="26">
         <v>4</v>
       </c>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="26">
+        <v>1</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="I5" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1665,19 +1699,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="28">
-        <v>1</v>
-      </c>
-      <c r="G6" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="28">
+        <v>1</v>
+      </c>
+      <c r="H6" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="I6" s="19" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1688,20 +1725,23 @@
       <c r="D7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="28">
-        <v>3</v>
-      </c>
-      <c r="F7" s="26">
-        <v>1</v>
-      </c>
-      <c r="G7" s="28" t="s">
+      <c r="E7" s="26">
+        <v>1</v>
+      </c>
+      <c r="F7" s="28">
+        <v>3</v>
+      </c>
+      <c r="G7" s="26">
+        <v>1</v>
+      </c>
+      <c r="H7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="I7" s="19" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1713,19 +1753,22 @@
         <v>22</v>
       </c>
       <c r="E8" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="28">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="28">
+        <v>1</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="I8" s="19" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1736,20 +1779,23 @@
       <c r="D9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="28">
-        <v>2</v>
-      </c>
-      <c r="F9" s="26">
-        <v>1</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="E9" s="26">
+        <v>1</v>
+      </c>
+      <c r="F9" s="28">
+        <v>2</v>
+      </c>
+      <c r="G9" s="26">
+        <v>1</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="I9" s="19" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1761,19 +1807,22 @@
         <v>26</v>
       </c>
       <c r="E10" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="28">
-        <v>1</v>
-      </c>
-      <c r="G10" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="28">
+        <v>1</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="I10" s="19" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1783,18 +1832,19 @@
       <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="9">
-        <v>2</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9">
+        <v>2</v>
+      </c>
+      <c r="G11" s="22">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="23"/>
-    </row>
-    <row r="12" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I11" s="23"/>
+    </row>
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1805,19 +1855,22 @@
         <v>30</v>
       </c>
       <c r="E12" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="28">
-        <v>1</v>
-      </c>
-      <c r="G12" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="28">
+        <v>1</v>
+      </c>
+      <c r="H12" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="I12" s="19" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1827,18 +1880,19 @@
       <c r="D13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="9">
-        <v>2</v>
-      </c>
-      <c r="F13" s="22">
-        <v>1</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9">
+        <v>2</v>
+      </c>
+      <c r="G13" s="22">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="23"/>
-    </row>
-    <row r="14" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I13" s="23"/>
+    </row>
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1849,19 +1903,22 @@
         <v>34</v>
       </c>
       <c r="E14" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="28">
         <v>2</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="28">
+        <v>2</v>
+      </c>
+      <c r="H14" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="I14" s="19" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1872,19 +1929,22 @@
         <v>37</v>
       </c>
       <c r="E15" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" s="28">
-        <v>2</v>
-      </c>
-      <c r="G15" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="28">
+        <v>2</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="I15" s="19" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -1894,17 +1954,18 @@
       <c r="D16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="11">
-        <v>2</v>
-      </c>
+      <c r="E16" s="11"/>
       <c r="F16" s="11">
         <v>2</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="11">
+        <v>2</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -1915,19 +1976,22 @@
         <v>41</v>
       </c>
       <c r="E17" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="28">
         <v>2</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="28">
+        <v>2</v>
+      </c>
+      <c r="H17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="I17" s="24" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -1937,17 +2001,18 @@
       <c r="D18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="11">
-        <v>2</v>
-      </c>
+      <c r="E18" s="11"/>
       <c r="F18" s="11">
         <v>2</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="11">
+        <v>2</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -1957,17 +2022,18 @@
       <c r="D19" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="11">
-        <v>2</v>
-      </c>
+      <c r="E19" s="11"/>
       <c r="F19" s="11">
         <v>2</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="11">
+        <v>2</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -1978,19 +2044,22 @@
         <v>47</v>
       </c>
       <c r="E20" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="28">
         <v>2</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="28">
+        <v>2</v>
+      </c>
+      <c r="H20" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="I20" s="19" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="28">
         <v>17</v>
       </c>
@@ -2001,19 +2070,22 @@
         <v>48</v>
       </c>
       <c r="E21" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="28">
+        <v>2</v>
+      </c>
+      <c r="G21" s="28">
         <v>4</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="H21" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="I21" s="19" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2024,19 +2096,22 @@
         <v>51</v>
       </c>
       <c r="E22" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="28">
-        <v>2</v>
-      </c>
-      <c r="G22" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="28">
+        <v>2</v>
+      </c>
+      <c r="H22" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="I22" s="19" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2046,17 +2121,18 @@
       <c r="D23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="11">
-        <v>2</v>
-      </c>
+      <c r="E23" s="11"/>
       <c r="F23" s="11">
         <v>2</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="11">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B24" s="11">
         <v>20</v>
       </c>
@@ -2066,17 +2142,18 @@
       <c r="D24" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="11">
-        <v>2</v>
-      </c>
+      <c r="E24" s="11"/>
       <c r="F24" s="11">
         <v>2</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="11">
+        <v>2</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2086,17 +2163,18 @@
       <c r="D25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="11">
-        <v>2</v>
-      </c>
+      <c r="E25" s="11"/>
       <c r="F25" s="11">
         <v>2</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="11">
+        <v>2</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2106,17 +2184,18 @@
       <c r="D26" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="11">
-        <v>2</v>
-      </c>
+      <c r="E26" s="11"/>
       <c r="F26" s="11">
         <v>2</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="11">
+        <v>2</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2127,19 +2206,22 @@
         <v>61</v>
       </c>
       <c r="E27" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="28">
         <v>2</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="28">
+        <v>2</v>
+      </c>
+      <c r="H27" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="I27" s="19" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2150,19 +2232,22 @@
         <v>63</v>
       </c>
       <c r="E28" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="28">
-        <v>2</v>
-      </c>
-      <c r="G28" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="28">
+        <v>2</v>
+      </c>
+      <c r="H28" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="I28" s="19" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="29" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2173,19 +2258,22 @@
         <v>65</v>
       </c>
       <c r="E29" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="28">
         <v>2</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="28">
+        <v>2</v>
+      </c>
+      <c r="H29" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="I29" s="19" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="30" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="28">
         <v>26</v>
       </c>
@@ -2196,19 +2284,22 @@
         <v>66</v>
       </c>
       <c r="E30" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="28">
         <v>2</v>
       </c>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="28">
+        <v>2</v>
+      </c>
+      <c r="H30" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="I30" s="19" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2218,17 +2309,18 @@
       <c r="D31" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="11">
-        <v>2</v>
-      </c>
+      <c r="E31" s="11"/>
       <c r="F31" s="11">
         <v>2</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="11">
+        <v>2</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B32" s="11">
         <v>28</v>
       </c>
@@ -2238,17 +2330,18 @@
       <c r="D32" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="11">
-        <v>2</v>
-      </c>
+      <c r="E32" s="11"/>
       <c r="F32" s="11">
-        <v>3</v>
-      </c>
-      <c r="G32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="11">
+        <v>3</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B33" s="11">
         <v>29</v>
       </c>
@@ -2258,17 +2351,18 @@
       <c r="D33" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="11">
-        <v>2</v>
-      </c>
+      <c r="E33" s="11"/>
       <c r="F33" s="11">
-        <v>3</v>
-      </c>
-      <c r="G33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="11">
+        <v>3</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2278,17 +2372,18 @@
       <c r="D34" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="11">
-        <v>2</v>
-      </c>
+      <c r="E34" s="11"/>
       <c r="F34" s="11">
-        <v>3</v>
-      </c>
-      <c r="G34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="11">
+        <v>3</v>
+      </c>
+      <c r="H34" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2298,17 +2393,18 @@
       <c r="D35" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="11">
-        <v>2</v>
-      </c>
+      <c r="E35" s="11"/>
       <c r="F35" s="11">
-        <v>3</v>
-      </c>
-      <c r="G35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="11">
+        <v>3</v>
+      </c>
+      <c r="H35" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2318,17 +2414,18 @@
       <c r="D36" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E36" s="11">
-        <v>2</v>
-      </c>
+      <c r="E36" s="11"/>
       <c r="F36" s="11">
-        <v>3</v>
-      </c>
-      <c r="G36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="11">
+        <v>3</v>
+      </c>
+      <c r="H36" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B37" s="11">
         <v>33</v>
       </c>
@@ -2338,17 +2435,18 @@
       <c r="D37" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="11"/>
+      <c r="F37" s="11">
         <v>4</v>
       </c>
-      <c r="F37" s="11">
-        <v>3</v>
-      </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="11">
+        <v>3</v>
+      </c>
+      <c r="H37" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B38" s="11">
         <v>34</v>
       </c>
@@ -2358,17 +2456,18 @@
       <c r="D38" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="11">
-        <v>2</v>
-      </c>
+      <c r="E38" s="11"/>
       <c r="F38" s="11">
-        <v>3</v>
-      </c>
-      <c r="G38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="11">
+        <v>3</v>
+      </c>
+      <c r="H38" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="2:8" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2379,19 +2478,22 @@
         <v>85</v>
       </c>
       <c r="E39" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="14">
         <v>2</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="14">
+        <v>2</v>
+      </c>
+      <c r="H39" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="I39" s="19" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="40" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2402,19 +2504,22 @@
         <v>87</v>
       </c>
       <c r="E40" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="14">
         <v>2</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="14">
+        <v>2</v>
+      </c>
+      <c r="H40" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="I40" s="19" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2425,19 +2530,22 @@
         <v>89</v>
       </c>
       <c r="E41" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="14">
         <v>2</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="14">
+        <v>2</v>
+      </c>
+      <c r="H41" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="I41" s="19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="42" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2448,19 +2556,22 @@
         <v>91</v>
       </c>
       <c r="E42" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="14">
         <v>2</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="I42" s="19" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="43" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2471,19 +2582,22 @@
         <v>93</v>
       </c>
       <c r="E43" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="14">
         <v>2</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="14">
+        <v>2</v>
+      </c>
+      <c r="H43" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="I43" s="19" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2494,19 +2608,22 @@
         <v>95</v>
       </c>
       <c r="E44" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="14">
-        <v>2</v>
-      </c>
-      <c r="G44" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="14">
+        <v>2</v>
+      </c>
+      <c r="H44" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="I44" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2517,19 +2634,22 @@
         <v>97</v>
       </c>
       <c r="E45" s="14">
+        <v>1</v>
+      </c>
+      <c r="F45" s="14">
         <v>4</v>
       </c>
-      <c r="F45" s="14">
-        <v>2</v>
-      </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="14">
+        <v>2</v>
+      </c>
+      <c r="H45" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="I45" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="46" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2540,19 +2660,22 @@
         <v>99</v>
       </c>
       <c r="E46" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="14">
-        <v>2</v>
-      </c>
-      <c r="G46" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="14">
+        <v>2</v>
+      </c>
+      <c r="H46" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="I46" s="19" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="47" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2563,19 +2686,22 @@
         <v>100</v>
       </c>
       <c r="E47" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="14">
-        <v>2</v>
-      </c>
-      <c r="G47" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="14">
+        <v>2</v>
+      </c>
+      <c r="H47" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H47" s="19" t="s">
+      <c r="I47" s="19" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="48" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2586,19 +2712,22 @@
         <v>102</v>
       </c>
       <c r="E48" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" s="14">
-        <v>2</v>
-      </c>
-      <c r="G48" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="14">
+        <v>2</v>
+      </c>
+      <c r="H48" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="I48" s="19" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2609,19 +2738,22 @@
         <v>104</v>
       </c>
       <c r="E49" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="14">
-        <v>2</v>
-      </c>
-      <c r="G49" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="14">
+        <v>2</v>
+      </c>
+      <c r="H49" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H49" s="19" t="s">
+      <c r="I49" s="19" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2632,19 +2764,22 @@
         <v>106</v>
       </c>
       <c r="E50" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="14">
-        <v>2</v>
-      </c>
-      <c r="G50" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="I50" s="19" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="51" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2655,19 +2790,22 @@
         <v>108</v>
       </c>
       <c r="E51" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" s="14">
-        <v>2</v>
-      </c>
-      <c r="G51" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G51" s="14">
+        <v>2</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="I51" s="19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="52" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2678,19 +2816,22 @@
         <v>110</v>
       </c>
       <c r="E52" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="14">
-        <v>2</v>
-      </c>
-      <c r="G52" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="14">
+        <v>2</v>
+      </c>
+      <c r="H52" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="I52" s="19" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="53" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2701,39 +2842,48 @@
         <v>112</v>
       </c>
       <c r="E53" s="14">
+        <v>1</v>
+      </c>
+      <c r="F53" s="14">
         <v>4</v>
       </c>
-      <c r="F53" s="14">
-        <v>2</v>
-      </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="14">
+        <v>2</v>
+      </c>
+      <c r="H53" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="I53" s="19" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="11">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="28">
         <v>50</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="E54" s="11">
-        <v>3</v>
-      </c>
-      <c r="F54" s="13">
-        <v>2</v>
-      </c>
-      <c r="G54" s="11" t="s">
+      <c r="E54" s="14">
+        <v>1</v>
+      </c>
+      <c r="F54" s="28">
+        <v>3</v>
+      </c>
+      <c r="G54" s="31">
+        <v>2</v>
+      </c>
+      <c r="H54" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="55" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I54" s="30" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2743,18 +2893,19 @@
       <c r="D55" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E55" s="9">
-        <v>2</v>
-      </c>
-      <c r="F55" s="13">
-        <v>2</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="E55" s="9"/>
+      <c r="F55" s="9">
+        <v>2</v>
+      </c>
+      <c r="G55" s="13">
+        <v>2</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H55" s="20"/>
-    </row>
-    <row r="56" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2764,18 +2915,19 @@
       <c r="D56" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="9">
-        <v>2</v>
-      </c>
-      <c r="F56" s="13">
-        <v>2</v>
-      </c>
-      <c r="G56" s="9" t="s">
+      <c r="E56" s="9"/>
+      <c r="F56" s="9">
+        <v>2</v>
+      </c>
+      <c r="G56" s="13">
+        <v>2</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H56" s="20"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="I56" s="20"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -2785,17 +2937,18 @@
       <c r="D57" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="11">
-        <v>2</v>
-      </c>
+      <c r="E57" s="11"/>
       <c r="F57" s="11">
-        <v>3</v>
-      </c>
-      <c r="G57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="11">
+        <v>3</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -2806,19 +2959,22 @@
         <v>121</v>
       </c>
       <c r="E58" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="28">
+        <v>3</v>
+      </c>
+      <c r="G58" s="28">
         <v>4</v>
       </c>
-      <c r="G58" s="28" t="s">
+      <c r="H58" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="I58" s="19" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="59" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -2829,19 +2985,22 @@
         <v>123</v>
       </c>
       <c r="E59" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="28">
+        <v>3</v>
+      </c>
+      <c r="G59" s="28">
         <v>4</v>
       </c>
-      <c r="G59" s="28" t="s">
+      <c r="H59" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H59" s="24" t="s">
+      <c r="I59" s="24" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="60" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -2852,19 +3011,22 @@
         <v>125</v>
       </c>
       <c r="E60" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="28">
+        <v>3</v>
+      </c>
+      <c r="G60" s="28">
         <v>4</v>
       </c>
-      <c r="G60" s="28" t="s">
+      <c r="H60" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H60" s="24" t="s">
+      <c r="I60" s="24" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="61" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -2875,19 +3037,22 @@
         <v>127</v>
       </c>
       <c r="E61" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="28">
+        <v>3</v>
+      </c>
+      <c r="G61" s="28">
         <v>4</v>
       </c>
-      <c r="G61" s="28" t="s">
+      <c r="H61" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H61" s="24" t="s">
+      <c r="I61" s="24" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="62" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -2898,19 +3063,22 @@
         <v>129</v>
       </c>
       <c r="E62" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F62" s="28">
         <v>4</v>
       </c>
-      <c r="G62" s="28" t="s">
+      <c r="G62" s="28">
+        <v>4</v>
+      </c>
+      <c r="H62" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="I62" s="19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="63" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -2921,19 +3089,22 @@
         <v>131</v>
       </c>
       <c r="E63" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="28">
+        <v>2</v>
+      </c>
+      <c r="G63" s="28">
         <v>4</v>
       </c>
-      <c r="G63" s="28" t="s">
+      <c r="H63" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="I63" s="19" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="64" spans="2:8" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -2944,19 +3115,22 @@
         <v>133</v>
       </c>
       <c r="E64" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="28">
+        <v>2</v>
+      </c>
+      <c r="G64" s="28">
         <v>4</v>
       </c>
-      <c r="G64" s="28" t="s">
+      <c r="H64" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="I64" s="19" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="65" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -2967,19 +3141,22 @@
         <v>135</v>
       </c>
       <c r="E65" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" s="28">
+        <v>3</v>
+      </c>
+      <c r="G65" s="28">
         <v>4</v>
       </c>
-      <c r="G65" s="28" t="s">
+      <c r="H65" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H65" s="19" t="s">
+      <c r="I65" s="19" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -2989,23 +3166,26 @@
       <c r="D66" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="14">
-        <v>4</v>
+      <c r="E66" s="28">
+        <v>1</v>
       </c>
       <c r="F66" s="14">
         <v>4</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" s="14">
+        <v>4</v>
+      </c>
+      <c r="H66" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H66" s="19" t="s">
+      <c r="I66" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I66" s="15" t="s">
+      <c r="J66" s="15" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="67" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3016,19 +3196,22 @@
         <v>138</v>
       </c>
       <c r="E67" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67" s="28">
         <v>4</v>
       </c>
-      <c r="G67" s="28" t="s">
+      <c r="G67" s="28">
+        <v>4</v>
+      </c>
+      <c r="H67" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H67" s="24" t="s">
+      <c r="I67" s="24" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3039,19 +3222,22 @@
         <v>140</v>
       </c>
       <c r="E68" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" s="28">
         <v>4</v>
       </c>
-      <c r="G68" s="28" t="s">
+      <c r="G68" s="28">
+        <v>4</v>
+      </c>
+      <c r="H68" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="I68" s="19" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="69" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3062,19 +3248,22 @@
         <v>142</v>
       </c>
       <c r="E69" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="28">
         <v>4</v>
       </c>
-      <c r="G69" s="28" t="s">
+      <c r="G69" s="28">
+        <v>4</v>
+      </c>
+      <c r="H69" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H69" s="19" t="s">
+      <c r="I69" s="19" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3085,19 +3274,22 @@
         <v>144</v>
       </c>
       <c r="E70" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" s="28">
+        <v>3</v>
+      </c>
+      <c r="G70" s="28">
         <v>4</v>
       </c>
-      <c r="G70" s="28" t="s">
+      <c r="H70" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H70" s="19" t="s">
+      <c r="I70" s="19" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B71" s="11">
         <v>67</v>
       </c>
@@ -3107,17 +3299,18 @@
       <c r="D71" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E71" s="11">
-        <v>3</v>
-      </c>
+      <c r="E71" s="11"/>
       <c r="F71" s="11">
+        <v>3</v>
+      </c>
+      <c r="G71" s="11">
         <v>4</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="H71" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="28">
         <v>68</v>
       </c>
@@ -3128,19 +3321,22 @@
         <v>147</v>
       </c>
       <c r="E72" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" s="28">
+        <v>3</v>
+      </c>
+      <c r="G72" s="28">
         <v>4</v>
       </c>
-      <c r="G72" s="28" t="s">
+      <c r="H72" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H72" s="19" t="s">
+      <c r="I72" s="19" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3150,17 +3346,18 @@
       <c r="D73" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E73" s="11">
-        <v>3</v>
-      </c>
+      <c r="E73" s="11"/>
       <c r="F73" s="11">
+        <v>3</v>
+      </c>
+      <c r="G73" s="11">
         <v>4</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="H73" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3170,17 +3367,18 @@
       <c r="D74" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E74" s="11">
-        <v>3</v>
-      </c>
+      <c r="E74" s="11"/>
       <c r="F74" s="11">
+        <v>3</v>
+      </c>
+      <c r="G74" s="11">
         <v>4</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="H74" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3190,17 +3388,18 @@
       <c r="D75" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E75" s="11">
-        <v>3</v>
-      </c>
+      <c r="E75" s="11"/>
       <c r="F75" s="11">
+        <v>3</v>
+      </c>
+      <c r="G75" s="11">
         <v>4</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="H75" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3210,17 +3409,18 @@
       <c r="D76" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E76" s="11">
-        <v>4</v>
-      </c>
+      <c r="E76" s="11"/>
       <c r="F76" s="11">
         <v>4</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="11">
+        <v>4</v>
+      </c>
+      <c r="H76" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="28">
         <v>73</v>
       </c>
@@ -3231,19 +3431,22 @@
         <v>155</v>
       </c>
       <c r="E77" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="28">
+        <v>2</v>
+      </c>
+      <c r="G77" s="28">
         <v>5</v>
       </c>
-      <c r="G77" s="28" t="s">
+      <c r="H77" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="I77" s="19" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3254,19 +3457,22 @@
         <v>158</v>
       </c>
       <c r="E78" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="28">
+        <v>2</v>
+      </c>
+      <c r="G78" s="28">
         <v>5</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="H78" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="I78" s="19" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="28">
         <v>75</v>
       </c>
@@ -3277,19 +3483,22 @@
         <v>159</v>
       </c>
       <c r="E79" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79" s="28">
+        <v>3</v>
+      </c>
+      <c r="G79" s="28">
         <v>5</v>
       </c>
-      <c r="G79" s="28" t="s">
+      <c r="H79" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="H79" s="24" t="s">
+      <c r="I79" s="24" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3299,18 +3508,19 @@
       <c r="D80" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E80" s="9">
-        <v>3</v>
-      </c>
-      <c r="F80" s="11">
+      <c r="E80" s="9"/>
+      <c r="F80" s="9">
+        <v>3</v>
+      </c>
+      <c r="G80" s="11">
         <v>5</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="H80" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H80" s="20"/>
-    </row>
-    <row r="81" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3320,18 +3530,19 @@
       <c r="D81" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E81" s="9">
-        <v>2</v>
-      </c>
-      <c r="F81" s="11">
+      <c r="E81" s="9"/>
+      <c r="F81" s="9">
+        <v>2</v>
+      </c>
+      <c r="G81" s="11">
         <v>5</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H81" s="20"/>
-    </row>
-    <row r="82" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I81" s="20"/>
+    </row>
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3341,18 +3552,19 @@
       <c r="D82" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E82" s="9">
-        <v>2</v>
-      </c>
-      <c r="F82" s="11">
+      <c r="E82" s="9"/>
+      <c r="F82" s="9">
+        <v>2</v>
+      </c>
+      <c r="G82" s="11">
         <v>5</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="H82" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H82" s="20"/>
-    </row>
-    <row r="83" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I82" s="20"/>
+    </row>
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3362,18 +3574,19 @@
       <c r="D83" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E83" s="9">
-        <v>2</v>
-      </c>
-      <c r="F83" s="11">
+      <c r="E83" s="9"/>
+      <c r="F83" s="9">
+        <v>2</v>
+      </c>
+      <c r="G83" s="11">
         <v>5</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="H83" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H83" s="20"/>
-    </row>
-    <row r="84" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I83" s="20"/>
+    </row>
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3384,19 +3597,22 @@
         <v>169</v>
       </c>
       <c r="E84" s="14">
-        <v>2</v>
-      </c>
-      <c r="F84" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="14">
+        <v>2</v>
+      </c>
+      <c r="G84" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="G84" s="14" t="s">
+      <c r="H84" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H84" s="19" t="s">
+      <c r="I84" s="19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="85" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3407,19 +3623,22 @@
         <v>171</v>
       </c>
       <c r="E85" s="14">
-        <v>2</v>
-      </c>
-      <c r="F85" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="14">
+        <v>2</v>
+      </c>
+      <c r="G85" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="H85" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H85" s="19" t="s">
+      <c r="I85" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3430,19 +3649,22 @@
         <v>173</v>
       </c>
       <c r="E86" s="14">
-        <v>2</v>
-      </c>
-      <c r="F86" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F86" s="14">
+        <v>2</v>
+      </c>
+      <c r="G86" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="H86" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H86" s="19" t="s">
+      <c r="I86" s="19" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="87" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3453,19 +3675,22 @@
         <v>174</v>
       </c>
       <c r="E87" s="14">
-        <v>2</v>
-      </c>
-      <c r="F87" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="14">
+        <v>2</v>
+      </c>
+      <c r="G87" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G87" s="14" t="s">
+      <c r="H87" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H87" s="19" t="s">
+      <c r="I87" s="19" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="88" spans="2:8" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3476,19 +3701,22 @@
         <v>176</v>
       </c>
       <c r="E88" s="14">
-        <v>2</v>
-      </c>
-      <c r="F88" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="14">
+        <v>2</v>
+      </c>
+      <c r="G88" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="H88" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H88" s="19" t="s">
+      <c r="I88" s="19" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="89" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3498,18 +3726,19 @@
       <c r="D89" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E89" s="9">
-        <v>2</v>
-      </c>
-      <c r="F89" s="10" t="s">
+      <c r="E89" s="9"/>
+      <c r="F89" s="9">
+        <v>2</v>
+      </c>
+      <c r="G89" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H89" s="20"/>
-    </row>
-    <row r="90" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I89" s="20"/>
+    </row>
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3519,18 +3748,19 @@
       <c r="D90" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="E90" s="9">
-        <v>2</v>
-      </c>
+      <c r="E90" s="9"/>
       <c r="F90" s="9">
+        <v>2</v>
+      </c>
+      <c r="G90" s="9">
         <v>6</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="H90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H90" s="20"/>
-    </row>
-    <row r="91" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I90" s="20"/>
+    </row>
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3540,18 +3770,19 @@
       <c r="D91" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E91" s="9">
-        <v>2</v>
-      </c>
+      <c r="E91" s="9"/>
       <c r="F91" s="9">
+        <v>2</v>
+      </c>
+      <c r="G91" s="9">
         <v>6</v>
       </c>
-      <c r="G91" s="9" t="s">
+      <c r="H91" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H91" s="20"/>
-    </row>
-    <row r="92" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I91" s="20"/>
+    </row>
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3561,18 +3792,19 @@
       <c r="D92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E92" s="9">
-        <v>3</v>
-      </c>
+      <c r="E92" s="9"/>
       <c r="F92" s="9">
+        <v>3</v>
+      </c>
+      <c r="G92" s="9">
         <v>7</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="H92" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H92" s="17"/>
-    </row>
-    <row r="93" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I92" s="17"/>
+    </row>
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3582,18 +3814,19 @@
       <c r="D93" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E93" s="9">
-        <v>3</v>
-      </c>
+      <c r="E93" s="9"/>
       <c r="F93" s="9">
+        <v>3</v>
+      </c>
+      <c r="G93" s="9">
         <v>7</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="H93" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H93" s="20"/>
-    </row>
-    <row r="94" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I93" s="20"/>
+    </row>
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3603,18 +3836,19 @@
       <c r="D94" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="E94" s="9">
-        <v>3</v>
-      </c>
+      <c r="E94" s="9"/>
       <c r="F94" s="9">
+        <v>3</v>
+      </c>
+      <c r="G94" s="9">
         <v>7</v>
       </c>
-      <c r="G94" s="9" t="s">
+      <c r="H94" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H94" s="20"/>
-    </row>
-    <row r="95" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I94" s="20"/>
+    </row>
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3624,18 +3858,19 @@
       <c r="D95" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="E95" s="9">
-        <v>3</v>
-      </c>
+      <c r="E95" s="9"/>
       <c r="F95" s="9">
+        <v>3</v>
+      </c>
+      <c r="G95" s="9">
         <v>7</v>
       </c>
-      <c r="G95" s="9" t="s">
+      <c r="H95" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="H95" s="20"/>
-    </row>
-    <row r="96" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I95" s="20"/>
+    </row>
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3645,18 +3880,19 @@
       <c r="D96" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E96" s="9">
-        <v>2</v>
-      </c>
+      <c r="E96" s="9"/>
       <c r="F96" s="9">
+        <v>2</v>
+      </c>
+      <c r="G96" s="9">
         <v>8</v>
       </c>
-      <c r="G96" s="9" t="s">
+      <c r="H96" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H96" s="20"/>
-    </row>
-    <row r="97" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I96" s="20"/>
+    </row>
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3666,18 +3902,19 @@
       <c r="D97" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="E97" s="9">
-        <v>2</v>
-      </c>
+      <c r="E97" s="9"/>
       <c r="F97" s="9">
+        <v>2</v>
+      </c>
+      <c r="G97" s="9">
         <v>8</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H97" s="20"/>
-    </row>
-    <row r="98" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I97" s="20"/>
+    </row>
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3687,18 +3924,19 @@
       <c r="D98" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="E98" s="9">
-        <v>2</v>
-      </c>
+      <c r="E98" s="9"/>
       <c r="F98" s="9">
+        <v>2</v>
+      </c>
+      <c r="G98" s="9">
         <v>8</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="H98" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H98" s="20"/>
-    </row>
-    <row r="99" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I98" s="20"/>
+    </row>
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -3708,18 +3946,19 @@
       <c r="D99" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E99" s="9">
-        <v>2</v>
-      </c>
+      <c r="E99" s="9"/>
       <c r="F99" s="9">
+        <v>2</v>
+      </c>
+      <c r="G99" s="9">
         <v>8</v>
       </c>
-      <c r="G99" s="9" t="s">
+      <c r="H99" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H99" s="20"/>
-    </row>
-    <row r="100" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I99" s="20"/>
+    </row>
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -3729,18 +3968,19 @@
       <c r="D100" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E100" s="9">
-        <v>2</v>
-      </c>
+      <c r="E100" s="9"/>
       <c r="F100" s="9">
+        <v>2</v>
+      </c>
+      <c r="G100" s="9">
         <v>8</v>
       </c>
-      <c r="G100" s="9" t="s">
+      <c r="H100" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H100" s="20"/>
-    </row>
-    <row r="101" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I100" s="20"/>
+    </row>
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -3750,18 +3990,19 @@
       <c r="D101" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E101" s="9">
-        <v>2</v>
-      </c>
+      <c r="E101" s="9"/>
       <c r="F101" s="9">
+        <v>2</v>
+      </c>
+      <c r="G101" s="9">
         <v>8</v>
       </c>
-      <c r="G101" s="9" t="s">
+      <c r="H101" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H101" s="20"/>
-    </row>
-    <row r="102" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I101" s="20"/>
+    </row>
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -3771,18 +4012,19 @@
       <c r="D102" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E102" s="9">
-        <v>2</v>
-      </c>
+      <c r="E102" s="9"/>
       <c r="F102" s="9">
+        <v>2</v>
+      </c>
+      <c r="G102" s="9">
         <v>8</v>
       </c>
-      <c r="G102" s="9" t="s">
+      <c r="H102" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H102" s="20"/>
-    </row>
-    <row r="103" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I102" s="20"/>
+    </row>
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -3792,18 +4034,19 @@
       <c r="D103" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E103" s="9">
-        <v>2</v>
-      </c>
+      <c r="E103" s="9"/>
       <c r="F103" s="9">
+        <v>2</v>
+      </c>
+      <c r="G103" s="9">
         <v>8</v>
       </c>
-      <c r="G103" s="9" t="s">
+      <c r="H103" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H103" s="20"/>
-    </row>
-    <row r="104" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I103" s="20"/>
+    </row>
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>
@@ -3813,16 +4056,17 @@
       <c r="D104" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E104" s="9">
-        <v>2</v>
-      </c>
+      <c r="E104" s="9"/>
       <c r="F104" s="9">
+        <v>2</v>
+      </c>
+      <c r="G104" s="9">
         <v>9</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="H104" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="H104" s="20"/>
+      <c r="I104" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B99C5-31D8-4372-861D-0E496078A287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242492B-A053-4653-8E14-B4BDE78578F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="284">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -999,6 +999,29 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[
+        {
+          "class": "TroopChangeSkillAttackRange",
+          "atkType": 5,
+          "atkRange": 1,
+          "conditon": {
+            "class": "SkillIdInList",
+            "ids": [
+              22,
+              23,
+              24,
+              25,
+              26,
+              27,
+              28
+            ],
+            "result": 1
+          }
+        }
+      ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3289,25 +3312,28 @@
         <v>272</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B71" s="11">
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
+      <c r="B71" s="28">
         <v>67</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11">
+      <c r="E71" s="28"/>
+      <c r="F71" s="28">
         <v>3</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="28">
         <v>4</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="28" t="s">
         <v>49</v>
+      </c>
+      <c r="I71" s="30" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2242492B-A053-4653-8E14-B4BDE78578F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7508934D-B80D-41EB-A7FF-327BDD8A86FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="289">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1022,6 +1022,26 @@
           }
         }
       ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeCaptiveFactor", value:100}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:1000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:1000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2155,25 +2175,28 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B24" s="11">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="28">
         <v>20</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11">
-        <v>2</v>
-      </c>
-      <c r="G24" s="11">
-        <v>2</v>
-      </c>
-      <c r="H24" s="11" t="s">
+      <c r="E24" s="28"/>
+      <c r="F24" s="28">
+        <v>2</v>
+      </c>
+      <c r="G24" s="28">
+        <v>2</v>
+      </c>
+      <c r="H24" s="28" t="s">
         <v>35</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.15">
@@ -2343,46 +2366,52 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B32" s="11">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="28">
         <v>28</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11">
-        <v>2</v>
-      </c>
-      <c r="G32" s="11">
+      <c r="E32" s="28"/>
+      <c r="F32" s="28">
+        <v>2</v>
+      </c>
+      <c r="G32" s="28">
         <v>3</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="28" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B33" s="11">
+      <c r="I32" s="19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="28">
         <v>29</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11">
-        <v>2</v>
-      </c>
-      <c r="G33" s="11">
+      <c r="E33" s="28"/>
+      <c r="F33" s="28">
+        <v>2</v>
+      </c>
+      <c r="G33" s="28">
         <v>3</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="28" t="s">
         <v>71</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.15">
@@ -2448,46 +2477,52 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B37" s="11">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="28">
         <v>33</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11">
+      <c r="E37" s="28"/>
+      <c r="F37" s="28">
         <v>4</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="28">
         <v>3</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="28" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B38" s="11">
+      <c r="I37" s="19" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="28">
         <v>34</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11">
-        <v>2</v>
-      </c>
-      <c r="G38" s="11">
+      <c r="E38" s="28"/>
+      <c r="F38" s="28">
+        <v>2</v>
+      </c>
+      <c r="G38" s="28">
         <v>3</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="28" t="s">
         <v>71</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7508934D-B80D-41EB-A7FF-327BDD8A86FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0F313D-954A-410F-91B5-441D2F2505C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1033,15 +1033,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:1000,operator:"lte"}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:1000,operator:"lte"}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2387,7 +2387,7 @@
         <v>71</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2411,7 +2411,7 @@
         <v>71</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.15">
@@ -2498,7 +2498,7 @@
         <v>71</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0F313D-954A-410F-91B5-441D2F2505C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBEFA7B-DA9C-4DF9-9E08-E321DE12163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>施展齐攻时，让对方陷入混乱</t>
   </si>
   <si>
-    <t>捕缚</t>
-  </si>
-  <si>
     <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
   </si>
   <si>
@@ -1002,12 +999,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>[{class:"TroopChangeCaptiveFactor", value:100}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[
         {
           "class": "TroopChangeSkillAttackRange",
           "atkType": 5,
           "atkRange": 1,
-          "conditon": {
+          "condition": {
             "class": "SkillIdInList",
             "ids": [
               22,
@@ -1025,23 +1034,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopChangeCaptiveFactor", value:100}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeEscapeFactor", value:200}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",value:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
+    <t>捕缚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1604,22 +1605,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1634,7 +1635,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1647,7 +1648,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1661,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1671,10 +1672,10 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="16" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1688,22 +1689,22 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1727,10 +1728,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1754,10 +1755,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1781,10 +1782,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1808,10 +1809,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1835,10 +1836,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1862,10 +1863,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1887,7 +1888,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1910,10 +1911,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1935,7 +1936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1958,10 +1959,10 @@
         <v>35</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1984,10 +1985,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2031,10 +2032,10 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2055,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2099,15 +2100,15 @@
         <v>35</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>48</v>
@@ -2125,10 +2126,10 @@
         <v>49</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2151,10 +2152,10 @@
         <v>35</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2175,15 +2176,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="28" t="s">
         <v>54</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>55</v>
       </c>
       <c r="E24" s="28"/>
       <c r="F24" s="28">
@@ -2196,18 +2197,18 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11">
@@ -2220,15 +2221,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11">
@@ -2241,15 +2242,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <v>23</v>
       </c>
       <c r="C27" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>60</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>61</v>
       </c>
       <c r="E27" s="28">
         <v>1</v>
@@ -2264,18 +2265,18 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <v>24</v>
       </c>
       <c r="C28" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="28" t="s">
         <v>62</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>63</v>
       </c>
       <c r="E28" s="28">
         <v>1</v>
@@ -2290,18 +2291,18 @@
         <v>35</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>25</v>
       </c>
       <c r="C29" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>64</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>65</v>
       </c>
       <c r="E29" s="28">
         <v>1</v>
@@ -2316,18 +2317,18 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" s="28">
         <v>1</v>
@@ -2342,18 +2343,18 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11">
@@ -2366,15 +2367,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <v>28</v>
       </c>
       <c r="C32" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="28" t="s">
         <v>69</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>70</v>
       </c>
       <c r="E32" s="28"/>
       <c r="F32" s="28">
@@ -2384,21 +2385,21 @@
         <v>3</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <v>29</v>
       </c>
       <c r="C33" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="28" t="s">
         <v>72</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>73</v>
       </c>
       <c r="E33" s="28"/>
       <c r="F33" s="28">
@@ -2408,21 +2409,21 @@
         <v>3</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11">
@@ -2432,18 +2433,18 @@
         <v>3</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="11">
@@ -2453,18 +2454,18 @@
         <v>3</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
       <c r="C36" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>79</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11">
@@ -2474,18 +2475,18 @@
         <v>3</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28">
         <v>33</v>
       </c>
       <c r="C37" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="E37" s="28"/>
       <c r="F37" s="28">
@@ -2495,21 +2496,21 @@
         <v>3</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28">
         <v>34</v>
       </c>
       <c r="C38" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="28" t="s">
         <v>82</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>83</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" s="28">
@@ -2519,21 +2520,21 @@
         <v>3</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <v>35</v>
       </c>
       <c r="C39" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="E39" s="14">
         <v>1</v>
@@ -2548,18 +2549,18 @@
         <v>35</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <v>36</v>
       </c>
       <c r="C40" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>87</v>
       </c>
       <c r="E40" s="14">
         <v>1</v>
@@ -2574,18 +2575,18 @@
         <v>35</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <v>37</v>
       </c>
       <c r="C41" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>89</v>
       </c>
       <c r="E41" s="14">
         <v>1</v>
@@ -2600,18 +2601,18 @@
         <v>35</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <v>38</v>
       </c>
       <c r="C42" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>91</v>
       </c>
       <c r="E42" s="14">
         <v>1</v>
@@ -2626,18 +2627,18 @@
         <v>35</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <v>39</v>
       </c>
       <c r="C43" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>93</v>
       </c>
       <c r="E43" s="14">
         <v>1</v>
@@ -2652,18 +2653,18 @@
         <v>35</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <v>40</v>
       </c>
       <c r="C44" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="E44" s="14">
         <v>1</v>
@@ -2678,18 +2679,18 @@
         <v>35</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <v>41</v>
       </c>
       <c r="C45" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="E45" s="14">
         <v>1</v>
@@ -2704,18 +2705,18 @@
         <v>35</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <v>42</v>
       </c>
       <c r="C46" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>98</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>99</v>
       </c>
       <c r="E46" s="14">
         <v>1</v>
@@ -2730,18 +2731,18 @@
         <v>35</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <v>43</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47" s="14">
         <v>1</v>
@@ -2756,18 +2757,18 @@
         <v>35</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <v>44</v>
       </c>
       <c r="C48" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="E48" s="14">
         <v>1</v>
@@ -2782,18 +2783,18 @@
         <v>35</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <v>45</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>104</v>
       </c>
       <c r="E49" s="14">
         <v>1</v>
@@ -2808,18 +2809,18 @@
         <v>35</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <v>46</v>
       </c>
       <c r="C50" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="E50" s="14">
         <v>1</v>
@@ -2834,18 +2835,18 @@
         <v>35</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <v>47</v>
       </c>
       <c r="C51" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="E51" s="14">
         <v>1</v>
@@ -2860,18 +2861,18 @@
         <v>35</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <v>48</v>
       </c>
       <c r="C52" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>110</v>
       </c>
       <c r="E52" s="14">
         <v>1</v>
@@ -2886,18 +2887,18 @@
         <v>35</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <v>49</v>
       </c>
       <c r="C53" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>111</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>112</v>
       </c>
       <c r="E53" s="14">
         <v>1</v>
@@ -2912,18 +2913,18 @@
         <v>35</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28">
         <v>50</v>
       </c>
       <c r="C54" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="28" t="s">
         <v>113</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>114</v>
       </c>
       <c r="E54" s="14">
         <v>1</v>
@@ -2938,18 +2939,18 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
       <c r="C55" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="9">
@@ -2963,15 +2964,15 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
       <c r="C56" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9">
@@ -2985,15 +2986,15 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="11">
@@ -3003,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3014,7 +3015,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E58" s="28">
         <v>1</v>
@@ -3029,18 +3030,18 @@
         <v>49</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28">
         <v>55</v>
       </c>
       <c r="C59" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" s="28" t="s">
         <v>122</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>123</v>
       </c>
       <c r="E59" s="28">
         <v>1</v>
@@ -3055,18 +3056,18 @@
         <v>49</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28">
         <v>56</v>
       </c>
       <c r="C60" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="28" t="s">
         <v>124</v>
-      </c>
-      <c r="D60" s="28" t="s">
-        <v>125</v>
       </c>
       <c r="E60" s="28">
         <v>1</v>
@@ -3081,18 +3082,18 @@
         <v>49</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28">
         <v>57</v>
       </c>
       <c r="C61" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" s="28" t="s">
         <v>126</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>127</v>
       </c>
       <c r="E61" s="28">
         <v>1</v>
@@ -3107,18 +3108,18 @@
         <v>49</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28">
         <v>58</v>
       </c>
       <c r="C62" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="28" t="s">
         <v>128</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>129</v>
       </c>
       <c r="E62" s="28">
         <v>1</v>
@@ -3133,18 +3134,18 @@
         <v>49</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28">
         <v>59</v>
       </c>
       <c r="C63" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="28" t="s">
         <v>130</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>131</v>
       </c>
       <c r="E63" s="28">
         <v>1</v>
@@ -3159,18 +3160,18 @@
         <v>49</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28">
         <v>60</v>
       </c>
       <c r="C64" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="28" t="s">
         <v>132</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>133</v>
       </c>
       <c r="E64" s="28">
         <v>1</v>
@@ -3185,18 +3186,18 @@
         <v>49</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28">
         <v>61</v>
       </c>
       <c r="C65" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="28" t="s">
         <v>134</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>135</v>
       </c>
       <c r="E65" s="28">
         <v>1</v>
@@ -3211,18 +3212,18 @@
         <v>49</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <v>62</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E66" s="28">
         <v>1</v>
@@ -3237,21 +3238,21 @@
         <v>49</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28">
         <v>63</v>
       </c>
       <c r="C67" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" s="28" t="s">
         <v>137</v>
-      </c>
-      <c r="D67" s="28" t="s">
-        <v>138</v>
       </c>
       <c r="E67" s="28">
         <v>1</v>
@@ -3266,18 +3267,18 @@
         <v>49</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28">
         <v>64</v>
       </c>
       <c r="C68" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" s="28" t="s">
         <v>139</v>
-      </c>
-      <c r="D68" s="28" t="s">
-        <v>140</v>
       </c>
       <c r="E68" s="28">
         <v>1</v>
@@ -3292,18 +3293,18 @@
         <v>49</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28">
         <v>65</v>
       </c>
       <c r="C69" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69" s="28" t="s">
         <v>141</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>142</v>
       </c>
       <c r="E69" s="28">
         <v>1</v>
@@ -3318,18 +3319,18 @@
         <v>49</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28">
         <v>66</v>
       </c>
       <c r="C70" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>143</v>
-      </c>
-      <c r="D70" s="28" t="s">
-        <v>144</v>
       </c>
       <c r="E70" s="28">
         <v>1</v>
@@ -3344,18 +3345,18 @@
         <v>49</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
       <c r="B71" s="28">
         <v>67</v>
       </c>
       <c r="C71" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="28" t="s">
         <v>145</v>
-      </c>
-      <c r="D71" s="28" t="s">
-        <v>146</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" s="28">
@@ -3368,18 +3369,18 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E72" s="28">
         <v>1</v>
@@ -3394,18 +3395,18 @@
         <v>49</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
       <c r="C73" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11">
@@ -3418,15 +3419,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11">
@@ -3439,15 +3440,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
       <c r="C75" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11">
@@ -3460,15 +3461,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>154</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="11">
@@ -3481,15 +3482,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="28">
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E77" s="28">
         <v>1</v>
@@ -3501,21 +3502,21 @@
         <v>5</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="28">
         <v>74</v>
       </c>
       <c r="C78" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D78" s="28" t="s">
         <v>157</v>
-      </c>
-      <c r="D78" s="28" t="s">
-        <v>158</v>
       </c>
       <c r="E78" s="28">
         <v>1</v>
@@ -3527,21 +3528,21 @@
         <v>5</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="28">
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E79" s="28">
         <v>1</v>
@@ -3553,21 +3554,21 @@
         <v>5</v>
       </c>
       <c r="H79" s="28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9">
         <v>76</v>
       </c>
       <c r="C80" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="E80" s="9"/>
       <c r="F80" s="9">
@@ -3577,19 +3578,19 @@
         <v>5</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9">
         <v>77</v>
       </c>
       <c r="C81" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>163</v>
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="9">
@@ -3599,19 +3600,19 @@
         <v>5</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
       <c r="C82" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9">
@@ -3621,19 +3622,19 @@
         <v>5</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
       <c r="C83" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9">
@@ -3643,20 +3644,20 @@
         <v>5</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <v>80</v>
       </c>
       <c r="C84" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D84" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D84" s="14" t="s">
-        <v>169</v>
-      </c>
       <c r="E84" s="14">
         <v>1</v>
       </c>
@@ -3664,25 +3665,25 @@
         <v>2</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <v>81</v>
       </c>
       <c r="C85" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D85" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D85" s="14" t="s">
-        <v>171</v>
-      </c>
       <c r="E85" s="14">
         <v>1</v>
       </c>
@@ -3690,25 +3691,25 @@
         <v>2</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <v>82</v>
       </c>
       <c r="C86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D86" s="14" t="s">
-        <v>173</v>
-      </c>
       <c r="E86" s="14">
         <v>1</v>
       </c>
@@ -3716,16 +3717,16 @@
         <v>2</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>8</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E87" s="14">
         <v>1</v>
@@ -3742,25 +3743,25 @@
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <v>84</v>
       </c>
       <c r="C88" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D88" s="14" t="s">
-        <v>176</v>
-      </c>
       <c r="E88" s="14">
         <v>1</v>
       </c>
@@ -3768,46 +3769,46 @@
         <v>2</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
       <c r="C89" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9">
         <v>2</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
       <c r="C90" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9">
@@ -3821,15 +3822,15 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
       <c r="C91" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9">
@@ -3843,15 +3844,15 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
       <c r="C92" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9">
@@ -3861,19 +3862,19 @@
         <v>7</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
       <c r="C93" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D93" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9">
@@ -3883,19 +3884,19 @@
         <v>7</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
       <c r="C94" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9">
@@ -3905,19 +3906,19 @@
         <v>7</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
       <c r="C95" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9">
@@ -3927,19 +3928,19 @@
         <v>7</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
       <c r="C96" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D96" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9">
@@ -3949,19 +3950,19 @@
         <v>8</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
       <c r="C97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9">
@@ -3971,19 +3972,19 @@
         <v>8</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
       <c r="C98" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9">
@@ -3993,19 +3994,19 @@
         <v>8</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
       <c r="C99" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D99" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9">
@@ -4015,19 +4016,19 @@
         <v>8</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
       <c r="C100" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>202</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9">
@@ -4037,19 +4038,19 @@
         <v>8</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
       <c r="C101" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9">
@@ -4059,19 +4060,19 @@
         <v>8</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
       <c r="C102" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9">
@@ -4081,19 +4082,19 @@
         <v>8</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
       <c r="C103" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9">
@@ -4103,19 +4104,19 @@
         <v>8</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>
       <c r="C104" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9">
@@ -4125,7 +4126,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I104" s="20"/>
     </row>
